--- a/research/traditional_assets/database/data/netherlands/netherlands_building_materials.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_building_materials.xlsx
@@ -1145,13 +1145,13 @@
         <v>19.7</v>
       </c>
       <c r="L2">
-        <v>23.4864435007901</v>
+        <v>23.48644350079</v>
       </c>
       <c r="M2">
         <v>45.91</v>
       </c>
       <c r="N2">
-        <v>44.7484435007901</v>
+        <v>44.74844350079</v>
       </c>
       <c r="O2">
         <v>27.7</v>
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08566264225687861</v>
+        <v>0.08547502263985587</v>
       </c>
       <c r="C2">
-        <v>41.57501824801674</v>
+        <v>41.2097934719772</v>
       </c>
       <c r="D2">
-        <v>40.08501824801674</v>
+        <v>40.19379347197719</v>
       </c>
       <c r="E2">
-        <v>-27.7</v>
+        <v>-27.226</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.474</v>
       </c>
       <c r="G2">
         <v>1.49</v>
@@ -1445,28 +1445,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0238422</v>
       </c>
       <c r="N2">
-        <v>5.753333333333334</v>
+        <v>5.729491133333334</v>
       </c>
       <c r="O2">
-        <v>1.48436</v>
+        <v>1.4782087124</v>
       </c>
       <c r="P2">
-        <v>4.268973333333333</v>
+        <v>4.251282420933334</v>
       </c>
       <c r="Q2">
-        <v>6.448973333333333</v>
+        <v>6.431282420933334</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08566264225687861</v>
+        <v>0.08596141074732916</v>
       </c>
       <c r="T2">
-        <v>0.9206152946161342</v>
+        <v>0.9275152597535602</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>241.3088277647757</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08547502263985587</v>
+        <v>0.08528740302283311</v>
       </c>
       <c r="C3">
-        <v>41.2097934719772</v>
+        <v>40.845160649981</v>
       </c>
       <c r="D3">
-        <v>40.19379347197719</v>
+        <v>40.303160649981</v>
       </c>
       <c r="E3">
-        <v>-27.226</v>
+        <v>-26.752</v>
       </c>
       <c r="F3">
-        <v>0.474</v>
+        <v>0.948</v>
       </c>
       <c r="G3">
         <v>1.49</v>
@@ -1527,28 +1527,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M3">
-        <v>0.0238422</v>
+        <v>0.04768439999999999</v>
       </c>
       <c r="N3">
-        <v>5.729491133333334</v>
+        <v>5.705648933333334</v>
       </c>
       <c r="O3">
-        <v>1.4782087124</v>
+        <v>1.4720574248</v>
       </c>
       <c r="P3">
-        <v>4.251282420933334</v>
+        <v>4.233591508533334</v>
       </c>
       <c r="Q3">
-        <v>6.431282420933334</v>
+        <v>6.413591508533335</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08596141074732916</v>
+        <v>0.08626627655391134</v>
       </c>
       <c r="T3">
-        <v>0.9275152597535602</v>
+        <v>0.9345560405060357</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>241.3088277647757</v>
+        <v>120.6544138823878</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08528740302283311</v>
+        <v>0.08509978340581036</v>
       </c>
       <c r="C4">
-        <v>40.845160649981</v>
+        <v>40.48112462732711</v>
       </c>
       <c r="D4">
-        <v>40.303160649981</v>
+        <v>40.4131246273271</v>
       </c>
       <c r="E4">
-        <v>-26.752</v>
+        <v>-26.278</v>
       </c>
       <c r="F4">
-        <v>0.948</v>
+        <v>1.422</v>
       </c>
       <c r="G4">
         <v>1.49</v>
@@ -1609,28 +1609,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M4">
-        <v>0.04768439999999999</v>
+        <v>0.0715266</v>
       </c>
       <c r="N4">
-        <v>5.705648933333334</v>
+        <v>5.681806733333334</v>
       </c>
       <c r="O4">
-        <v>1.4720574248</v>
+        <v>1.4659061372</v>
       </c>
       <c r="P4">
-        <v>4.233591508533334</v>
+        <v>4.215900596133333</v>
       </c>
       <c r="Q4">
-        <v>6.413591508533335</v>
+        <v>6.395900596133334</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08626627655391134</v>
+        <v>0.08657742825341275</v>
       </c>
       <c r="T4">
-        <v>0.9345560405060357</v>
+        <v>0.9417419919956755</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>120.6544138823878</v>
+        <v>80.43627592159189</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08509978340581036</v>
+        <v>0.08491216378878763</v>
       </c>
       <c r="C5">
-        <v>40.48112462732711</v>
+        <v>40.1176903023392</v>
       </c>
       <c r="D5">
-        <v>40.4131246273271</v>
+        <v>40.5236903023392</v>
       </c>
       <c r="E5">
-        <v>-26.278</v>
+        <v>-25.804</v>
       </c>
       <c r="F5">
-        <v>1.422</v>
+        <v>1.896</v>
       </c>
       <c r="G5">
         <v>1.49</v>
@@ -1691,28 +1691,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M5">
-        <v>0.0715266</v>
+        <v>0.09536879999999999</v>
       </c>
       <c r="N5">
-        <v>5.681806733333334</v>
+        <v>5.657964533333334</v>
       </c>
       <c r="O5">
-        <v>1.4659061372</v>
+        <v>1.4597548496</v>
       </c>
       <c r="P5">
-        <v>4.215900596133333</v>
+        <v>4.198209683733333</v>
       </c>
       <c r="Q5">
-        <v>6.395900596133334</v>
+        <v>6.378209683733333</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08657742825341275</v>
+        <v>0.08689506227998711</v>
       </c>
       <c r="T5">
-        <v>0.9417419919956755</v>
+        <v>0.9490776508080164</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>80.43627592159189</v>
+        <v>60.32720694119391</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08491216378878763</v>
+        <v>0.08472454417176487</v>
       </c>
       <c r="C6">
-        <v>40.1176903023392</v>
+        <v>39.75486262709312</v>
       </c>
       <c r="D6">
-        <v>40.5236903023392</v>
+        <v>40.63486262709311</v>
       </c>
       <c r="E6">
-        <v>-25.804</v>
+        <v>-25.33</v>
       </c>
       <c r="F6">
-        <v>1.896</v>
+        <v>2.37</v>
       </c>
       <c r="G6">
         <v>1.49</v>
@@ -1773,28 +1773,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M6">
-        <v>0.09536879999999999</v>
+        <v>0.119211</v>
       </c>
       <c r="N6">
-        <v>5.657964533333334</v>
+        <v>5.634122333333334</v>
       </c>
       <c r="O6">
-        <v>1.4597548496</v>
+        <v>1.453603562</v>
       </c>
       <c r="P6">
-        <v>4.198209683733333</v>
+        <v>4.180518771333333</v>
       </c>
       <c r="Q6">
-        <v>6.378209683733333</v>
+        <v>6.360518771333334</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08689506227998711</v>
+        <v>0.08721938333869987</v>
       </c>
       <c r="T6">
-        <v>0.9490776508080164</v>
+        <v>0.9565677445427223</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>60.32720694119391</v>
+        <v>48.26176555295513</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08472454417176487</v>
+        <v>0.08453692455474211</v>
       </c>
       <c r="C7">
-        <v>39.75486262709312</v>
+        <v>39.39264660815599</v>
       </c>
       <c r="D7">
-        <v>40.63486262709311</v>
+        <v>40.74664660815599</v>
       </c>
       <c r="E7">
-        <v>-25.33</v>
+        <v>-24.856</v>
       </c>
       <c r="F7">
-        <v>2.37</v>
+        <v>2.844</v>
       </c>
       <c r="G7">
         <v>1.49</v>
@@ -1855,28 +1855,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M7">
-        <v>0.119211</v>
+        <v>0.1430532</v>
       </c>
       <c r="N7">
-        <v>5.634122333333334</v>
+        <v>5.610280133333334</v>
       </c>
       <c r="O7">
-        <v>1.453603562</v>
+        <v>1.4474522744</v>
       </c>
       <c r="P7">
-        <v>4.180518771333333</v>
+        <v>4.162827858933333</v>
       </c>
       <c r="Q7">
-        <v>6.360518771333334</v>
+        <v>6.342827858933333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08721938333869987</v>
+        <v>0.08755060484547034</v>
       </c>
       <c r="T7">
-        <v>0.9565677445427223</v>
+        <v>0.9642172019739111</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>48.26176555295513</v>
+        <v>40.21813796079594</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08453692455474211</v>
+        <v>0.08434930493771939</v>
       </c>
       <c r="C8">
-        <v>39.39264660815599</v>
+        <v>39.03104730733799</v>
       </c>
       <c r="D8">
-        <v>40.74664660815599</v>
+        <v>40.85904730733799</v>
       </c>
       <c r="E8">
-        <v>-24.856</v>
+        <v>-24.382</v>
       </c>
       <c r="F8">
-        <v>2.844</v>
+        <v>3.318</v>
       </c>
       <c r="G8">
         <v>1.49</v>
@@ -1937,28 +1937,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M8">
-        <v>0.1430532</v>
+        <v>0.1668954</v>
       </c>
       <c r="N8">
-        <v>5.610280133333334</v>
+        <v>5.586437933333334</v>
       </c>
       <c r="O8">
-        <v>1.4474522744</v>
+        <v>1.4413009868</v>
       </c>
       <c r="P8">
-        <v>4.162827858933333</v>
+        <v>4.145136946533334</v>
       </c>
       <c r="Q8">
-        <v>6.342827858933333</v>
+        <v>6.325136946533334</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08755060484547034</v>
+        <v>0.08788894939539718</v>
       </c>
       <c r="T8">
-        <v>0.9642172019739111</v>
+        <v>0.9720311638659859</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>40.21813796079594</v>
+        <v>34.47268968068224</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08434930493771937</v>
+        <v>0.08416168532069664</v>
       </c>
       <c r="C9">
-        <v>39.031047307338</v>
+        <v>38.67006984245638</v>
       </c>
       <c r="D9">
-        <v>40.859047307338</v>
+        <v>40.97206984245638</v>
       </c>
       <c r="E9">
-        <v>-24.382</v>
+        <v>-23.908</v>
       </c>
       <c r="F9">
-        <v>3.318</v>
+        <v>3.792</v>
       </c>
       <c r="G9">
         <v>1.49</v>
@@ -2019,28 +2019,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M9">
-        <v>0.1668954</v>
+        <v>0.1907376</v>
       </c>
       <c r="N9">
-        <v>5.586437933333334</v>
+        <v>5.562595733333334</v>
       </c>
       <c r="O9">
-        <v>1.4413009868</v>
+        <v>1.4351496992</v>
       </c>
       <c r="P9">
-        <v>4.145136946533334</v>
+        <v>4.127446034133333</v>
       </c>
       <c r="Q9">
-        <v>6.325136946533334</v>
+        <v>6.307446034133333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08788894939539718</v>
+        <v>0.08823464926162677</v>
       </c>
       <c r="T9">
-        <v>0.9720311638659859</v>
+        <v>0.9800149944948447</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>34.47268968068224</v>
+        <v>30.16360347059696</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08416168532069664</v>
+        <v>0.08397406570367388</v>
       </c>
       <c r="C10">
-        <v>38.67006984245638</v>
+        <v>38.30971938811216</v>
       </c>
       <c r="D10">
-        <v>40.97206984245638</v>
+        <v>41.08571938811215</v>
       </c>
       <c r="E10">
-        <v>-23.908</v>
+        <v>-23.434</v>
       </c>
       <c r="F10">
-        <v>3.792</v>
+        <v>4.266</v>
       </c>
       <c r="G10">
         <v>1.49</v>
@@ -2101,28 +2101,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M10">
-        <v>0.1907376</v>
+        <v>0.2145798</v>
       </c>
       <c r="N10">
-        <v>5.562595733333334</v>
+        <v>5.538753533333334</v>
       </c>
       <c r="O10">
-        <v>1.4351496992</v>
+        <v>1.4289984116</v>
       </c>
       <c r="P10">
-        <v>4.127446034133333</v>
+        <v>4.109755121733333</v>
       </c>
       <c r="Q10">
-        <v>6.307446034133333</v>
+        <v>6.289755121733334</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08823464926162677</v>
+        <v>0.08858794692711416</v>
       </c>
       <c r="T10">
-        <v>0.9800149944948447</v>
+        <v>0.9881742939287336</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>30.16360347059696</v>
+        <v>26.81209197386396</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08397406570367388</v>
+        <v>0.08378644608665113</v>
       </c>
       <c r="C11">
-        <v>38.30971938811216</v>
+        <v>37.95000117647991</v>
       </c>
       <c r="D11">
-        <v>41.08571938811215</v>
+        <v>41.20000117647991</v>
       </c>
       <c r="E11">
-        <v>-23.434</v>
+        <v>-22.96</v>
       </c>
       <c r="F11">
-        <v>4.266</v>
+        <v>4.739999999999999</v>
       </c>
       <c r="G11">
         <v>1.49</v>
@@ -2183,28 +2183,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M11">
-        <v>0.2145798</v>
+        <v>0.238422</v>
       </c>
       <c r="N11">
-        <v>5.538753533333334</v>
+        <v>5.514911333333334</v>
       </c>
       <c r="O11">
-        <v>1.4289984116</v>
+        <v>1.422847124</v>
       </c>
       <c r="P11">
-        <v>4.109755121733333</v>
+        <v>4.092064209333333</v>
       </c>
       <c r="Q11">
-        <v>6.289755121733334</v>
+        <v>6.272064209333333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08858794692711416</v>
+        <v>0.08894909565183459</v>
       </c>
       <c r="T11">
-        <v>0.9881742939287336</v>
+        <v>0.9965149111278201</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>26.81209197386396</v>
+        <v>24.13088277647757</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08378644608665113</v>
+        <v>0.08359882646962839</v>
       </c>
       <c r="C12">
-        <v>37.95000117647991</v>
+        <v>37.59092049811071</v>
       </c>
       <c r="D12">
-        <v>41.20000117647991</v>
+        <v>41.31492049811071</v>
       </c>
       <c r="E12">
-        <v>-22.96</v>
+        <v>-22.486</v>
       </c>
       <c r="F12">
-        <v>4.74</v>
+        <v>5.214</v>
       </c>
       <c r="G12">
         <v>1.49</v>
@@ -2265,28 +2265,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M12">
-        <v>0.238422</v>
+        <v>0.2622641999999999</v>
       </c>
       <c r="N12">
-        <v>5.514911333333334</v>
+        <v>5.491069133333334</v>
       </c>
       <c r="O12">
-        <v>1.422847124</v>
+        <v>1.4166958364</v>
       </c>
       <c r="P12">
-        <v>4.092064209333333</v>
+        <v>4.074373296933334</v>
       </c>
       <c r="Q12">
-        <v>6.272064209333333</v>
+        <v>6.254373296933334</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08894909565183459</v>
+        <v>0.08931836007823414</v>
       </c>
       <c r="T12">
-        <v>0.9965149111278201</v>
+        <v>1.005042957926886</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.13088277647757</v>
+        <v>21.93716616043416</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08359882646962839</v>
+        <v>0.08341120685260565</v>
       </c>
       <c r="C13">
-        <v>37.59092049811071</v>
+        <v>37.23248270274857</v>
       </c>
       <c r="D13">
-        <v>41.31492049811071</v>
+        <v>41.43048270274857</v>
       </c>
       <c r="E13">
-        <v>-22.486</v>
+        <v>-22.012</v>
       </c>
       <c r="F13">
-        <v>5.214</v>
+        <v>5.688</v>
       </c>
       <c r="G13">
         <v>1.49</v>
@@ -2347,28 +2347,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M13">
-        <v>0.2622641999999999</v>
+        <v>0.2861064</v>
       </c>
       <c r="N13">
-        <v>5.491069133333334</v>
+        <v>5.467226933333334</v>
       </c>
       <c r="O13">
-        <v>1.4166958364</v>
+        <v>1.4105445488</v>
       </c>
       <c r="P13">
-        <v>4.074373296933334</v>
+        <v>4.056682384533334</v>
       </c>
       <c r="Q13">
-        <v>6.254373296933334</v>
+        <v>6.236682384533333</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08931836007823414</v>
+        <v>0.08969601687796097</v>
       </c>
       <c r="T13">
-        <v>1.005042957926886</v>
+        <v>1.013764823971385</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>21.93716616043416</v>
+        <v>20.10906898039797</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08341120685260565</v>
+        <v>0.0832235872355829</v>
       </c>
       <c r="C14">
-        <v>37.23248270274857</v>
+        <v>36.8746932001606</v>
       </c>
       <c r="D14">
-        <v>41.43048270274857</v>
+        <v>41.5466932001606</v>
       </c>
       <c r="E14">
-        <v>-22.012</v>
+        <v>-21.538</v>
       </c>
       <c r="F14">
-        <v>5.688</v>
+        <v>6.162</v>
       </c>
       <c r="G14">
         <v>1.49</v>
@@ -2429,28 +2429,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M14">
-        <v>0.2861064</v>
+        <v>0.3099486</v>
       </c>
       <c r="N14">
-        <v>5.467226933333334</v>
+        <v>5.443384733333334</v>
       </c>
       <c r="O14">
-        <v>1.4105445488</v>
+        <v>1.4043932612</v>
       </c>
       <c r="P14">
-        <v>4.056682384533334</v>
+        <v>4.038991472133334</v>
       </c>
       <c r="Q14">
-        <v>6.236682384533333</v>
+        <v>6.218991472133334</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08969601687796097</v>
+        <v>0.09008235544319873</v>
       </c>
       <c r="T14">
-        <v>1.013764823971385</v>
+        <v>1.022687192683574</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.10906898039797</v>
+        <v>18.56221752036736</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0832235872355829</v>
+        <v>0.08303596761856016</v>
       </c>
       <c r="C15">
-        <v>36.8746932001606</v>
+        <v>36.51755746098113</v>
       </c>
       <c r="D15">
-        <v>41.5466932001606</v>
+        <v>41.66355746098113</v>
       </c>
       <c r="E15">
-        <v>-21.538</v>
+        <v>-21.064</v>
       </c>
       <c r="F15">
-        <v>6.162</v>
+        <v>6.636</v>
       </c>
       <c r="G15">
         <v>1.49</v>
@@ -2511,28 +2511,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M15">
-        <v>0.3099486</v>
+        <v>0.3337908</v>
       </c>
       <c r="N15">
-        <v>5.443384733333334</v>
+        <v>5.419542533333334</v>
       </c>
       <c r="O15">
-        <v>1.4043932612</v>
+        <v>1.3982419736</v>
       </c>
       <c r="P15">
-        <v>4.038991472133334</v>
+        <v>4.021300559733334</v>
       </c>
       <c r="Q15">
-        <v>6.218991472133334</v>
+        <v>6.201300559733333</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09008235544319873</v>
+        <v>0.09047767862623274</v>
       </c>
       <c r="T15">
-        <v>1.022687192683574</v>
+        <v>1.031817058342557</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.56221752036736</v>
+        <v>17.23634484034112</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08303596761856016</v>
+        <v>0.0828483480015374</v>
       </c>
       <c r="C16">
-        <v>36.51755746098113</v>
+        <v>36.16108101757031</v>
       </c>
       <c r="D16">
-        <v>41.66355746098113</v>
+        <v>41.78108101757031</v>
       </c>
       <c r="E16">
-        <v>-21.064</v>
+        <v>-20.59</v>
       </c>
       <c r="F16">
-        <v>6.636</v>
+        <v>7.110000000000001</v>
       </c>
       <c r="G16">
         <v>1.49</v>
@@ -2593,28 +2593,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M16">
-        <v>0.3337908</v>
+        <v>0.357633</v>
       </c>
       <c r="N16">
-        <v>5.419542533333334</v>
+        <v>5.395700333333334</v>
       </c>
       <c r="O16">
-        <v>1.3982419736</v>
+        <v>1.392090686</v>
       </c>
       <c r="P16">
-        <v>4.021300559733334</v>
+        <v>4.003609647333334</v>
       </c>
       <c r="Q16">
-        <v>6.201300559733333</v>
+        <v>6.183609647333334</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09047767862623274</v>
+        <v>0.09088230353122048</v>
       </c>
       <c r="T16">
-        <v>1.031817058342557</v>
+        <v>1.041161744369988</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.23634484034112</v>
+        <v>16.08725518431837</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0828483480015374</v>
+        <v>0.08266072838451466</v>
       </c>
       <c r="C17">
-        <v>36.16108101757031</v>
+        <v>35.80526946488695</v>
       </c>
       <c r="D17">
-        <v>41.78108101757031</v>
+        <v>41.89926946488695</v>
       </c>
       <c r="E17">
-        <v>-20.59</v>
+        <v>-20.116</v>
       </c>
       <c r="F17">
-        <v>7.109999999999999</v>
+        <v>7.584</v>
       </c>
       <c r="G17">
         <v>1.49</v>
@@ -2675,28 +2675,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M17">
-        <v>0.357633</v>
+        <v>0.3814752</v>
       </c>
       <c r="N17">
-        <v>5.395700333333334</v>
+        <v>5.371858133333334</v>
       </c>
       <c r="O17">
-        <v>1.392090686</v>
+        <v>1.3859393984</v>
       </c>
       <c r="P17">
-        <v>4.003609647333334</v>
+        <v>3.985918734933334</v>
       </c>
       <c r="Q17">
-        <v>6.183609647333334</v>
+        <v>6.165918734933333</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09088230353122048</v>
+        <v>0.09129656236251746</v>
       </c>
       <c r="T17">
-        <v>1.041161744369988</v>
+        <v>1.050728922921881</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.08725518431838</v>
+        <v>15.08180173529848</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08266072838451466</v>
+        <v>0.08247310876749192</v>
       </c>
       <c r="C18">
-        <v>35.80526946488695</v>
+        <v>35.4501284613766</v>
       </c>
       <c r="D18">
-        <v>41.89926946488695</v>
+        <v>42.0181284613766</v>
       </c>
       <c r="E18">
-        <v>-20.116</v>
+        <v>-19.642</v>
       </c>
       <c r="F18">
-        <v>7.584</v>
+        <v>8.058</v>
       </c>
       <c r="G18">
         <v>1.49</v>
@@ -2757,28 +2757,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M18">
-        <v>0.3814752</v>
+        <v>0.4053174</v>
       </c>
       <c r="N18">
-        <v>5.371858133333334</v>
+        <v>5.348015933333333</v>
       </c>
       <c r="O18">
-        <v>1.3859393984</v>
+        <v>1.3797881108</v>
       </c>
       <c r="P18">
-        <v>3.985918734933334</v>
+        <v>3.968227822533334</v>
       </c>
       <c r="Q18">
-        <v>6.165918734933333</v>
+        <v>6.148227822533334</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09129656236251746</v>
+        <v>0.09172080333432761</v>
       </c>
       <c r="T18">
-        <v>1.050728922921881</v>
+        <v>1.060526635896712</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.08180173529848</v>
+        <v>14.19463692733974</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08247310876749192</v>
+        <v>0.08228548915046915</v>
       </c>
       <c r="C19">
-        <v>35.4501284613766</v>
+        <v>35.09566372987452</v>
       </c>
       <c r="D19">
-        <v>42.0181284613766</v>
+        <v>42.13766372987452</v>
       </c>
       <c r="E19">
-        <v>-19.642</v>
+        <v>-19.168</v>
       </c>
       <c r="F19">
-        <v>8.058</v>
+        <v>8.532</v>
       </c>
       <c r="G19">
         <v>1.49</v>
@@ -2839,28 +2839,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M19">
-        <v>0.4053174</v>
+        <v>0.4291596</v>
       </c>
       <c r="N19">
-        <v>5.348015933333333</v>
+        <v>5.324173733333334</v>
       </c>
       <c r="O19">
-        <v>1.3797881108</v>
+        <v>1.3736368232</v>
       </c>
       <c r="P19">
-        <v>3.968227822533334</v>
+        <v>3.950536910133334</v>
       </c>
       <c r="Q19">
-        <v>6.148227822533334</v>
+        <v>6.130536910133333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09172080333432761</v>
+        <v>0.09215539164691361</v>
       </c>
       <c r="T19">
-        <v>1.060526635896712</v>
+        <v>1.070563317480684</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.19463692733974</v>
+        <v>13.40604598693198</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08228548915046915</v>
+        <v>0.08230933953344642</v>
       </c>
       <c r="C20">
-        <v>35.09566372987452</v>
+        <v>34.60643057379057</v>
       </c>
       <c r="D20">
-        <v>42.13766372987452</v>
+        <v>42.12243057379057</v>
       </c>
       <c r="E20">
-        <v>-19.168</v>
+        <v>-18.694</v>
       </c>
       <c r="F20">
-        <v>8.532</v>
+        <v>9.006</v>
       </c>
       <c r="G20">
         <v>1.49</v>
@@ -2921,45 +2921,45 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M20">
-        <v>0.4291596</v>
+        <v>0.4665108</v>
       </c>
       <c r="N20">
-        <v>5.324173733333334</v>
+        <v>5.286822533333334</v>
       </c>
       <c r="O20">
-        <v>1.3736368232</v>
+        <v>1.3640002136</v>
       </c>
       <c r="P20">
-        <v>3.950536910133334</v>
+        <v>3.922822319733334</v>
       </c>
       <c r="Q20">
-        <v>6.130536910133333</v>
+        <v>6.102822319733334</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09215539164691361</v>
+        <v>0.09260071053511904</v>
       </c>
       <c r="T20">
-        <v>1.070563317480684</v>
+        <v>1.080847818363026</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.258</v>
       </c>
       <c r="W20">
-        <v>0.0373226</v>
+        <v>0.0384356</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>13.40604598693198</v>
+        <v>12.3326905472142</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08230933953344642</v>
+        <v>0.08213284991642367</v>
       </c>
       <c r="C21">
-        <v>34.60643057379057</v>
+        <v>34.24541537147549</v>
       </c>
       <c r="D21">
-        <v>42.12243057379057</v>
+        <v>42.23541537147549</v>
       </c>
       <c r="E21">
-        <v>-18.694</v>
+        <v>-18.22</v>
       </c>
       <c r="F21">
-        <v>9.006</v>
+        <v>9.48</v>
       </c>
       <c r="G21">
         <v>1.49</v>
@@ -3003,28 +3003,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M21">
-        <v>0.4665108</v>
+        <v>0.491064</v>
       </c>
       <c r="N21">
-        <v>5.286822533333334</v>
+        <v>5.262269333333334</v>
       </c>
       <c r="O21">
-        <v>1.3640002136</v>
+        <v>1.357665488</v>
       </c>
       <c r="P21">
-        <v>3.922822319733334</v>
+        <v>3.904603845333334</v>
       </c>
       <c r="Q21">
-        <v>6.102822319733334</v>
+        <v>6.084603845333334</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09260071053511904</v>
+        <v>0.09305716239552958</v>
       </c>
       <c r="T21">
-        <v>1.080847818363026</v>
+        <v>1.091389431767427</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>12.3326905472142</v>
+        <v>11.71605601985349</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08213284991642367</v>
+        <v>0.08195636029940093</v>
       </c>
       <c r="C22">
-        <v>34.24541537147549</v>
+        <v>33.88500791650256</v>
       </c>
       <c r="D22">
-        <v>42.23541537147549</v>
+        <v>42.34900791650256</v>
       </c>
       <c r="E22">
-        <v>-18.22</v>
+        <v>-17.746</v>
       </c>
       <c r="F22">
-        <v>9.48</v>
+        <v>9.954000000000001</v>
       </c>
       <c r="G22">
         <v>1.49</v>
@@ -3085,28 +3085,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M22">
-        <v>0.491064</v>
+        <v>0.5156172</v>
       </c>
       <c r="N22">
-        <v>5.262269333333334</v>
+        <v>5.237716133333334</v>
       </c>
       <c r="O22">
-        <v>1.357665488</v>
+        <v>1.3513307624</v>
       </c>
       <c r="P22">
-        <v>3.904603845333334</v>
+        <v>3.886385370933334</v>
       </c>
       <c r="Q22">
-        <v>6.084603845333334</v>
+        <v>6.066385370933334</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09305716239552958</v>
+        <v>0.09352516999924168</v>
       </c>
       <c r="T22">
-        <v>1.091389431767427</v>
+        <v>1.102197921460547</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.71605601985349</v>
+        <v>11.15814859033666</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08195636029940091</v>
+        <v>0.08177987068237817</v>
       </c>
       <c r="C23">
-        <v>33.88500791650257</v>
+        <v>33.52521312572221</v>
       </c>
       <c r="D23">
-        <v>42.34900791650257</v>
+        <v>42.46321312572221</v>
       </c>
       <c r="E23">
-        <v>-17.746</v>
+        <v>-17.272</v>
       </c>
       <c r="F23">
-        <v>9.953999999999999</v>
+        <v>10.428</v>
       </c>
       <c r="G23">
         <v>1.49</v>
@@ -3167,28 +3167,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M23">
-        <v>0.5156171999999999</v>
+        <v>0.5401703999999999</v>
       </c>
       <c r="N23">
-        <v>5.237716133333334</v>
+        <v>5.213162933333334</v>
       </c>
       <c r="O23">
-        <v>1.3513307624</v>
+        <v>1.3449960368</v>
       </c>
       <c r="P23">
-        <v>3.886385370933334</v>
+        <v>3.868166896533333</v>
       </c>
       <c r="Q23">
-        <v>6.066385370933334</v>
+        <v>6.048166896533333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09352516999924167</v>
+        <v>0.09400517779792074</v>
       </c>
       <c r="T23">
-        <v>1.102197921460547</v>
+        <v>1.113283551915029</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.15814859033666</v>
+        <v>10.65096001804863</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08177987068237817</v>
+        <v>0.08160338106535543</v>
       </c>
       <c r="C24">
-        <v>33.52521312572221</v>
+        <v>33.16603596916655</v>
       </c>
       <c r="D24">
-        <v>42.46321312572221</v>
+        <v>42.57803596916655</v>
       </c>
       <c r="E24">
-        <v>-17.272</v>
+        <v>-16.798</v>
       </c>
       <c r="F24">
-        <v>10.428</v>
+        <v>10.902</v>
       </c>
       <c r="G24">
         <v>1.49</v>
@@ -3249,28 +3249,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M24">
-        <v>0.5401703999999999</v>
+        <v>0.5647236</v>
       </c>
       <c r="N24">
-        <v>5.213162933333334</v>
+        <v>5.188609733333334</v>
       </c>
       <c r="O24">
-        <v>1.3449960368</v>
+        <v>1.3386613112</v>
       </c>
       <c r="P24">
-        <v>3.868166896533333</v>
+        <v>3.849948422133334</v>
       </c>
       <c r="Q24">
-        <v>6.048166896533333</v>
+        <v>6.029948422133334</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09400517779792074</v>
+        <v>0.09449765333163043</v>
       </c>
       <c r="T24">
-        <v>1.113283551915029</v>
+        <v>1.124657120822874</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.65096001804863</v>
+        <v>10.1878747998726</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08160338106535543</v>
+        <v>0.08172962744833269</v>
       </c>
       <c r="C25">
-        <v>33.16603596916655</v>
+        <v>32.6098378984634</v>
       </c>
       <c r="D25">
-        <v>42.57803596916655</v>
+        <v>42.4958378984634</v>
       </c>
       <c r="E25">
-        <v>-16.798</v>
+        <v>-16.324</v>
       </c>
       <c r="F25">
-        <v>10.902</v>
+        <v>11.376</v>
       </c>
       <c r="G25">
         <v>1.49</v>
@@ -3331,45 +3331,45 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M25">
-        <v>0.5647236</v>
+        <v>0.608616</v>
       </c>
       <c r="N25">
-        <v>5.188609733333334</v>
+        <v>5.144717333333334</v>
       </c>
       <c r="O25">
-        <v>1.3386613112</v>
+        <v>1.327337072</v>
       </c>
       <c r="P25">
-        <v>3.849948422133334</v>
+        <v>3.817380261333334</v>
       </c>
       <c r="Q25">
-        <v>6.029948422133334</v>
+        <v>5.997380261333334</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09449765333163043</v>
+        <v>0.09500308874780616</v>
       </c>
       <c r="T25">
-        <v>1.124657120822874</v>
+        <v>1.136329994175662</v>
       </c>
       <c r="U25">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.258</v>
       </c>
       <c r="W25">
-        <v>0.0384356</v>
+        <v>0.039697</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>10.1878747998726</v>
+        <v>9.453141773028205</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08172962744833269</v>
+        <v>0.08156575183130993</v>
       </c>
       <c r="C26">
-        <v>32.6098378984634</v>
+        <v>32.2425976306704</v>
       </c>
       <c r="D26">
-        <v>42.4958378984634</v>
+        <v>42.6025976306704</v>
       </c>
       <c r="E26">
-        <v>-16.324</v>
+        <v>-15.85</v>
       </c>
       <c r="F26">
-        <v>11.376</v>
+        <v>11.85</v>
       </c>
       <c r="G26">
         <v>1.49</v>
@@ -3413,28 +3413,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M26">
-        <v>0.6086159999999999</v>
+        <v>0.633975</v>
       </c>
       <c r="N26">
-        <v>5.144717333333334</v>
+        <v>5.119358333333334</v>
       </c>
       <c r="O26">
-        <v>1.327337072</v>
+        <v>1.32079445</v>
       </c>
       <c r="P26">
-        <v>3.817380261333334</v>
+        <v>3.798563883333334</v>
       </c>
       <c r="Q26">
-        <v>5.997380261333334</v>
+        <v>5.978563883333335</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09500308874780616</v>
+        <v>0.09552200244174658</v>
       </c>
       <c r="T26">
-        <v>1.136329994175662</v>
+        <v>1.148314144151191</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.453141773028205</v>
+        <v>9.075016102107078</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08156575183130993</v>
+        <v>0.08140187621428718</v>
       </c>
       <c r="C27">
-        <v>32.2425976306704</v>
+        <v>31.87589512594815</v>
       </c>
       <c r="D27">
-        <v>42.6025976306704</v>
+        <v>42.70989512594815</v>
       </c>
       <c r="E27">
-        <v>-15.85</v>
+        <v>-15.376</v>
       </c>
       <c r="F27">
-        <v>11.85</v>
+        <v>12.324</v>
       </c>
       <c r="G27">
         <v>1.49</v>
@@ -3495,28 +3495,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M27">
-        <v>0.633975</v>
+        <v>0.659334</v>
       </c>
       <c r="N27">
-        <v>5.119358333333334</v>
+        <v>5.093999333333334</v>
       </c>
       <c r="O27">
-        <v>1.32079445</v>
+        <v>1.314251828</v>
       </c>
       <c r="P27">
-        <v>3.798563883333334</v>
+        <v>3.779747505333333</v>
       </c>
       <c r="Q27">
-        <v>5.978563883333335</v>
+        <v>5.959747505333334</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09552200244174658</v>
+        <v>0.09605494083011781</v>
       </c>
       <c r="T27">
-        <v>1.148314144151191</v>
+        <v>1.160622190072005</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.075016102107078</v>
+        <v>8.725977021256805</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08140187621428718</v>
+        <v>0.08123800059726445</v>
       </c>
       <c r="C28">
-        <v>31.87589512594815</v>
+        <v>31.50973445773282</v>
       </c>
       <c r="D28">
-        <v>42.70989512594815</v>
+        <v>42.81773445773282</v>
       </c>
       <c r="E28">
-        <v>-15.376</v>
+        <v>-14.902</v>
       </c>
       <c r="F28">
-        <v>12.324</v>
+        <v>12.798</v>
       </c>
       <c r="G28">
         <v>1.49</v>
@@ -3577,28 +3577,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M28">
-        <v>0.659334</v>
+        <v>0.684693</v>
       </c>
       <c r="N28">
-        <v>5.093999333333334</v>
+        <v>5.068640333333334</v>
       </c>
       <c r="O28">
-        <v>1.314251828</v>
+        <v>1.307709206</v>
       </c>
       <c r="P28">
-        <v>3.779747505333333</v>
+        <v>3.760931127333333</v>
       </c>
       <c r="Q28">
-        <v>5.959747505333334</v>
+        <v>5.940931127333334</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09605494083011781</v>
+        <v>0.09660248027022528</v>
       </c>
       <c r="T28">
-        <v>1.160622190072005</v>
+        <v>1.173267442730376</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.725977021256805</v>
+        <v>8.402792687136181</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08123800059726445</v>
+        <v>0.08107412498024169</v>
       </c>
       <c r="C29">
-        <v>31.50973445773282</v>
+        <v>31.14411974070522</v>
       </c>
       <c r="D29">
-        <v>42.81773445773282</v>
+        <v>42.92611974070522</v>
       </c>
       <c r="E29">
-        <v>-14.902</v>
+        <v>-14.428</v>
       </c>
       <c r="F29">
-        <v>12.798</v>
+        <v>13.272</v>
       </c>
       <c r="G29">
         <v>1.49</v>
@@ -3659,28 +3659,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M29">
-        <v>0.684693</v>
+        <v>0.710052</v>
       </c>
       <c r="N29">
-        <v>5.068640333333334</v>
+        <v>5.043281333333334</v>
       </c>
       <c r="O29">
-        <v>1.307709206</v>
+        <v>1.301166584</v>
       </c>
       <c r="P29">
-        <v>3.760931127333333</v>
+        <v>3.742114749333334</v>
       </c>
       <c r="Q29">
-        <v>5.940931127333334</v>
+        <v>5.922114749333334</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09660248027022528</v>
+        <v>0.09716522913922458</v>
       </c>
       <c r="T29">
-        <v>1.173267442730376</v>
+        <v>1.186263952407034</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.402792687136181</v>
+        <v>8.10269294830989</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08107412498024169</v>
+        <v>0.08091024936321894</v>
       </c>
       <c r="C30">
-        <v>31.14411974070522</v>
+        <v>30.77905513131407</v>
       </c>
       <c r="D30">
-        <v>42.92611974070522</v>
+        <v>43.03505513131407</v>
       </c>
       <c r="E30">
-        <v>-14.428</v>
+        <v>-13.954</v>
       </c>
       <c r="F30">
-        <v>13.272</v>
+        <v>13.746</v>
       </c>
       <c r="G30">
         <v>1.49</v>
@@ -3741,28 +3741,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M30">
-        <v>0.710052</v>
+        <v>0.735411</v>
       </c>
       <c r="N30">
-        <v>5.043281333333334</v>
+        <v>5.017922333333334</v>
       </c>
       <c r="O30">
-        <v>1.301166584</v>
+        <v>1.294623962</v>
       </c>
       <c r="P30">
-        <v>3.742114749333334</v>
+        <v>3.723298371333334</v>
       </c>
       <c r="Q30">
-        <v>5.922114749333334</v>
+        <v>5.903298371333333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09716522913922458</v>
+        <v>0.09774383008904078</v>
       </c>
       <c r="T30">
-        <v>1.186263952407034</v>
+        <v>1.199626560947824</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.10269294830989</v>
+        <v>7.823289743195756</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08091024936321894</v>
+        <v>0.0809244537461962</v>
       </c>
       <c r="C31">
-        <v>30.77905513131408</v>
+        <v>30.29559096769713</v>
       </c>
       <c r="D31">
-        <v>43.03505513131407</v>
+        <v>43.02559096769713</v>
       </c>
       <c r="E31">
-        <v>-13.954</v>
+        <v>-13.48</v>
       </c>
       <c r="F31">
-        <v>13.746</v>
+        <v>14.22</v>
       </c>
       <c r="G31">
         <v>1.49</v>
@@ -3823,45 +3823,45 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M31">
-        <v>0.7354109999999999</v>
+        <v>0.772146</v>
       </c>
       <c r="N31">
-        <v>5.017922333333334</v>
+        <v>4.981187333333334</v>
       </c>
       <c r="O31">
-        <v>1.294623962</v>
+        <v>1.285146332</v>
       </c>
       <c r="P31">
-        <v>3.723298371333334</v>
+        <v>3.696041001333334</v>
       </c>
       <c r="Q31">
-        <v>5.903298371333333</v>
+        <v>5.876041001333334</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09774383008904078</v>
+        <v>0.098338962494566</v>
       </c>
       <c r="T31">
-        <v>1.199626560947824</v>
+        <v>1.213370958304065</v>
       </c>
       <c r="U31">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V31">
         <v>0.258</v>
       </c>
       <c r="W31">
-        <v>0.039697</v>
+        <v>0.0402906</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y31">
-        <v>7.823289743195756</v>
+        <v>7.451095172847277</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0809244537461962</v>
+        <v>0.08076651412917345</v>
       </c>
       <c r="C32">
-        <v>30.29559096769713</v>
+        <v>29.92705847939999</v>
       </c>
       <c r="D32">
-        <v>43.02559096769713</v>
+        <v>43.13105847939999</v>
       </c>
       <c r="E32">
-        <v>-13.48</v>
+        <v>-13.006</v>
       </c>
       <c r="F32">
-        <v>14.22</v>
+        <v>14.694</v>
       </c>
       <c r="G32">
         <v>1.49</v>
@@ -3905,28 +3905,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M32">
-        <v>0.772146</v>
+        <v>0.7978841999999999</v>
       </c>
       <c r="N32">
-        <v>4.981187333333334</v>
+        <v>4.955449133333333</v>
       </c>
       <c r="O32">
-        <v>1.285146332</v>
+        <v>1.2785058764</v>
       </c>
       <c r="P32">
-        <v>3.696041001333334</v>
+        <v>3.676943256933333</v>
       </c>
       <c r="Q32">
-        <v>5.876041001333334</v>
+        <v>5.856943256933334</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.098338962494566</v>
+        <v>0.09895134511474414</v>
       </c>
       <c r="T32">
-        <v>1.213370958304065</v>
+        <v>1.227513743989472</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.451095172847277</v>
+        <v>7.210737264045752</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08076651412917345</v>
+        <v>0.08060857451215071</v>
       </c>
       <c r="C33">
-        <v>29.92705847939999</v>
+        <v>29.55904432120672</v>
       </c>
       <c r="D33">
-        <v>43.13105847939999</v>
+        <v>43.23704432120672</v>
       </c>
       <c r="E33">
-        <v>-13.006</v>
+        <v>-12.532</v>
       </c>
       <c r="F33">
-        <v>14.694</v>
+        <v>15.168</v>
       </c>
       <c r="G33">
         <v>1.49</v>
@@ -3987,28 +3987,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M33">
-        <v>0.7978841999999999</v>
+        <v>0.8236224</v>
       </c>
       <c r="N33">
-        <v>4.955449133333333</v>
+        <v>4.929710933333334</v>
       </c>
       <c r="O33">
-        <v>1.2785058764</v>
+        <v>1.2718654208</v>
       </c>
       <c r="P33">
-        <v>3.676943256933333</v>
+        <v>3.657845512533334</v>
       </c>
       <c r="Q33">
-        <v>5.856943256933334</v>
+        <v>5.837845512533335</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09895134511474414</v>
+        <v>0.09958173898845693</v>
       </c>
       <c r="T33">
-        <v>1.227513743989472</v>
+        <v>1.242072493959745</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.210737264045752</v>
+        <v>6.985401724544323</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08060857451215071</v>
+        <v>0.08045063489512795</v>
       </c>
       <c r="C34">
-        <v>29.55904432120672</v>
+        <v>29.1915523236038</v>
       </c>
       <c r="D34">
-        <v>43.23704432120672</v>
+        <v>43.3435523236038</v>
       </c>
       <c r="E34">
-        <v>-12.532</v>
+        <v>-12.058</v>
       </c>
       <c r="F34">
-        <v>15.168</v>
+        <v>15.642</v>
       </c>
       <c r="G34">
         <v>1.49</v>
@@ -4069,28 +4069,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M34">
-        <v>0.8236224</v>
+        <v>0.8493606</v>
       </c>
       <c r="N34">
-        <v>4.929710933333334</v>
+        <v>4.903972733333334</v>
       </c>
       <c r="O34">
-        <v>1.2718654208</v>
+        <v>1.2652249652</v>
       </c>
       <c r="P34">
-        <v>3.657845512533334</v>
+        <v>3.638747768133334</v>
       </c>
       <c r="Q34">
-        <v>5.837845512533335</v>
+        <v>5.818747768133334</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09958173898845693</v>
+        <v>0.1002309505897432</v>
       </c>
       <c r="T34">
-        <v>1.242072493959745</v>
+        <v>1.257065833481368</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.985401724544323</v>
+        <v>6.773722884406616</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08045063489512795</v>
+        <v>0.0802926952781052</v>
       </c>
       <c r="C35">
-        <v>29.1915523236038</v>
+        <v>28.82458635491415</v>
       </c>
       <c r="D35">
-        <v>43.3435523236038</v>
+        <v>43.45058635491414</v>
       </c>
       <c r="E35">
-        <v>-12.058</v>
+        <v>-11.584</v>
       </c>
       <c r="F35">
-        <v>15.642</v>
+        <v>16.116</v>
       </c>
       <c r="G35">
         <v>1.49</v>
@@ -4151,28 +4151,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M35">
-        <v>0.8493606</v>
+        <v>0.8750988</v>
       </c>
       <c r="N35">
-        <v>4.903972733333334</v>
+        <v>4.878234533333334</v>
       </c>
       <c r="O35">
-        <v>1.2652249652</v>
+        <v>1.2585845096</v>
       </c>
       <c r="P35">
-        <v>3.638747768133334</v>
+        <v>3.619650023733334</v>
       </c>
       <c r="Q35">
-        <v>5.818747768133334</v>
+        <v>5.799650023733333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1002309505897432</v>
+        <v>0.1008998352698564</v>
       </c>
       <c r="T35">
-        <v>1.257065833481368</v>
+        <v>1.272513516624859</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.773722884406616</v>
+        <v>6.574495740747598</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0802926952781052</v>
+        <v>0.08013475566108247</v>
       </c>
       <c r="C36">
-        <v>28.82458635491415</v>
+        <v>28.4581503217656</v>
       </c>
       <c r="D36">
-        <v>43.45058635491414</v>
+        <v>43.55815032176559</v>
       </c>
       <c r="E36">
-        <v>-11.584</v>
+        <v>-11.11</v>
       </c>
       <c r="F36">
-        <v>16.116</v>
+        <v>16.59</v>
       </c>
       <c r="G36">
         <v>1.49</v>
@@ -4233,28 +4233,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M36">
-        <v>0.8750988</v>
+        <v>0.900837</v>
       </c>
       <c r="N36">
-        <v>4.878234533333334</v>
+        <v>4.852496333333334</v>
       </c>
       <c r="O36">
-        <v>1.2585845096</v>
+        <v>1.251944054</v>
       </c>
       <c r="P36">
-        <v>3.619650023733334</v>
+        <v>3.600552279333334</v>
       </c>
       <c r="Q36">
-        <v>5.799650023733333</v>
+        <v>5.780552279333333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1008998352698564</v>
+        <v>0.10158930101705</v>
       </c>
       <c r="T36">
-        <v>1.272513516624859</v>
+        <v>1.288436513095842</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.574495740747598</v>
+        <v>6.386653005297666</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08013475566108247</v>
+        <v>0.07997681604405971</v>
       </c>
       <c r="C37">
-        <v>28.4581503217656</v>
+        <v>28.09224816956618</v>
       </c>
       <c r="D37">
-        <v>43.55815032176559</v>
+        <v>43.66624816956617</v>
       </c>
       <c r="E37">
-        <v>-11.11</v>
+        <v>-10.636</v>
       </c>
       <c r="F37">
-        <v>16.59</v>
+        <v>17.064</v>
       </c>
       <c r="G37">
         <v>1.49</v>
@@ -4315,28 +4315,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M37">
-        <v>0.900837</v>
+        <v>0.9265752</v>
       </c>
       <c r="N37">
-        <v>4.852496333333334</v>
+        <v>4.826758133333334</v>
       </c>
       <c r="O37">
-        <v>1.251944054</v>
+        <v>1.2453035984</v>
       </c>
       <c r="P37">
-        <v>3.600552279333334</v>
+        <v>3.581454534933334</v>
       </c>
       <c r="Q37">
-        <v>5.780552279333333</v>
+        <v>5.761454534933334</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.10158930101705</v>
+        <v>0.1023003125688433</v>
       </c>
       <c r="T37">
-        <v>1.288436513095842</v>
+        <v>1.304857103206543</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.386653005297666</v>
+        <v>6.20924597737273</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07997681604405972</v>
+        <v>0.08009341642703698</v>
       </c>
       <c r="C38">
-        <v>28.09224816956616</v>
+        <v>27.53839219087773</v>
       </c>
       <c r="D38">
-        <v>43.66624816956616</v>
+        <v>43.58639219087772</v>
       </c>
       <c r="E38">
-        <v>-10.636</v>
+        <v>-10.162</v>
       </c>
       <c r="F38">
-        <v>17.064</v>
+        <v>17.538</v>
       </c>
       <c r="G38">
         <v>1.49</v>
@@ -4397,45 +4397,45 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M38">
-        <v>0.9265752</v>
+        <v>0.9698514</v>
       </c>
       <c r="N38">
-        <v>4.826758133333334</v>
+        <v>4.783481933333334</v>
       </c>
       <c r="O38">
-        <v>1.2453035984</v>
+        <v>1.2341383388</v>
       </c>
       <c r="P38">
-        <v>3.581454534933334</v>
+        <v>3.549343594533334</v>
       </c>
       <c r="Q38">
-        <v>5.761454534933334</v>
+        <v>5.729343594533335</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1023003125688433</v>
+        <v>0.1030338959159317</v>
       </c>
       <c r="T38">
-        <v>1.304857103206543</v>
+        <v>1.321798981892187</v>
       </c>
       <c r="U38">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V38">
         <v>0.258</v>
       </c>
       <c r="W38">
-        <v>0.0402906</v>
+        <v>0.0410326</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>6.20924597737273</v>
+        <v>5.932180263216956</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08009341642703698</v>
+        <v>0.07994289681001422</v>
       </c>
       <c r="C39">
-        <v>27.53839219087773</v>
+        <v>27.1675333699795</v>
       </c>
       <c r="D39">
-        <v>43.58639219087772</v>
+        <v>43.6895333699795</v>
       </c>
       <c r="E39">
-        <v>-10.162</v>
+        <v>-9.687999999999999</v>
       </c>
       <c r="F39">
-        <v>17.538</v>
+        <v>18.012</v>
       </c>
       <c r="G39">
         <v>1.49</v>
@@ -4479,28 +4479,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M39">
-        <v>0.9698514</v>
+        <v>0.9960636</v>
       </c>
       <c r="N39">
-        <v>4.783481933333334</v>
+        <v>4.757269733333334</v>
       </c>
       <c r="O39">
-        <v>1.2341383388</v>
+        <v>1.2273755912</v>
       </c>
       <c r="P39">
-        <v>3.549343594533334</v>
+        <v>3.529894142133333</v>
       </c>
       <c r="Q39">
-        <v>5.729343594533335</v>
+        <v>5.709894142133333</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1030338959159317</v>
+        <v>0.1037911432419584</v>
       </c>
       <c r="T39">
-        <v>1.321798981892187</v>
+        <v>1.339287372793498</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.932180263216956</v>
+        <v>5.776070256290194</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07994289681001422</v>
+        <v>0.07979237719299148</v>
       </c>
       <c r="C40">
-        <v>27.1675333699795</v>
+        <v>26.79716384565311</v>
       </c>
       <c r="D40">
-        <v>43.6895333699795</v>
+        <v>43.79316384565311</v>
       </c>
       <c r="E40">
-        <v>-9.687999999999999</v>
+        <v>-9.213999999999999</v>
       </c>
       <c r="F40">
-        <v>18.012</v>
+        <v>18.486</v>
       </c>
       <c r="G40">
         <v>1.49</v>
@@ -4561,28 +4561,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M40">
-        <v>0.9960636</v>
+        <v>1.0222758</v>
       </c>
       <c r="N40">
-        <v>4.757269733333334</v>
+        <v>4.731057533333334</v>
       </c>
       <c r="O40">
-        <v>1.2273755912</v>
+        <v>1.2206128436</v>
       </c>
       <c r="P40">
-        <v>3.529894142133333</v>
+        <v>3.510444689733334</v>
       </c>
       <c r="Q40">
-        <v>5.709894142133333</v>
+        <v>5.690444689733334</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1037911432419584</v>
+        <v>0.1045732183491664</v>
       </c>
       <c r="T40">
-        <v>1.339287372793498</v>
+        <v>1.357349153560424</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.776070256290194</v>
+        <v>5.627965890744292</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07979237719299148</v>
+        <v>0.07964185757596874</v>
       </c>
       <c r="C41">
-        <v>26.79716384565311</v>
+        <v>26.42728710797448</v>
       </c>
       <c r="D41">
-        <v>43.79316384565311</v>
+        <v>43.89728710797448</v>
       </c>
       <c r="E41">
-        <v>-9.213999999999999</v>
+        <v>-8.739999999999998</v>
       </c>
       <c r="F41">
-        <v>18.486</v>
+        <v>18.96</v>
       </c>
       <c r="G41">
         <v>1.49</v>
@@ -4643,28 +4643,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M41">
-        <v>1.0222758</v>
+        <v>1.048488</v>
       </c>
       <c r="N41">
-        <v>4.731057533333334</v>
+        <v>4.704845333333334</v>
       </c>
       <c r="O41">
-        <v>1.2206128436</v>
+        <v>1.213850096</v>
       </c>
       <c r="P41">
-        <v>3.510444689733334</v>
+        <v>3.490995237333334</v>
       </c>
       <c r="Q41">
-        <v>5.690444689733334</v>
+        <v>5.670995237333334</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1045732183491664</v>
+        <v>0.1053813626266146</v>
       </c>
       <c r="T41">
-        <v>1.357349153560424</v>
+        <v>1.376012993686249</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.627965890744292</v>
+        <v>5.487266743475685</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07964185757596874</v>
+        <v>0.07949133795894599</v>
       </c>
       <c r="C42">
-        <v>26.42728710797448</v>
+        <v>26.05790668029084</v>
       </c>
       <c r="D42">
-        <v>43.89728710797448</v>
+        <v>44.00190668029084</v>
       </c>
       <c r="E42">
-        <v>-8.739999999999998</v>
+        <v>-8.265999999999998</v>
       </c>
       <c r="F42">
-        <v>18.96</v>
+        <v>19.434</v>
       </c>
       <c r="G42">
         <v>1.49</v>
@@ -4725,28 +4725,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M42">
-        <v>1.048488</v>
+        <v>1.0747002</v>
       </c>
       <c r="N42">
-        <v>4.704845333333334</v>
+        <v>4.678633133333333</v>
       </c>
       <c r="O42">
-        <v>1.213850096</v>
+        <v>1.2070873484</v>
       </c>
       <c r="P42">
-        <v>3.490995237333334</v>
+        <v>3.471545784933333</v>
       </c>
       <c r="Q42">
-        <v>5.670995237333334</v>
+        <v>5.651545784933333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1053813626266146</v>
+        <v>0.1062169016253322</v>
       </c>
       <c r="T42">
-        <v>1.376012993686249</v>
+        <v>1.395309506358711</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.487266743475685</v>
+        <v>5.353430969244569</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07949133795894599</v>
+        <v>0.07934081834192323</v>
       </c>
       <c r="C43">
-        <v>26.05790668029084</v>
+        <v>25.68902611961818</v>
       </c>
       <c r="D43">
-        <v>44.00190668029084</v>
+        <v>44.10702611961818</v>
       </c>
       <c r="E43">
-        <v>-8.265999999999998</v>
+        <v>-7.791999999999998</v>
       </c>
       <c r="F43">
-        <v>19.434</v>
+        <v>19.908</v>
       </c>
       <c r="G43">
         <v>1.49</v>
@@ -4807,28 +4807,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M43">
-        <v>1.0747002</v>
+        <v>1.1009124</v>
       </c>
       <c r="N43">
-        <v>4.678633133333333</v>
+        <v>4.652420933333334</v>
       </c>
       <c r="O43">
-        <v>1.2070873484</v>
+        <v>1.2003246008</v>
       </c>
       <c r="P43">
-        <v>3.471545784933333</v>
+        <v>3.452096332533333</v>
       </c>
       <c r="Q43">
-        <v>5.651545784933333</v>
+        <v>5.632096332533333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1062169016253322</v>
+        <v>0.1070812523136608</v>
       </c>
       <c r="T43">
-        <v>1.395309506358711</v>
+        <v>1.415271416019879</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.353430969244569</v>
+        <v>5.225968327119699</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07934081834192325</v>
+        <v>0.07919029872490049</v>
       </c>
       <c r="C44">
-        <v>25.68902611961817</v>
+        <v>25.32064901704432</v>
       </c>
       <c r="D44">
-        <v>44.10702611961816</v>
+        <v>44.21264901704432</v>
       </c>
       <c r="E44">
-        <v>-7.792000000000002</v>
+        <v>-7.318000000000001</v>
       </c>
       <c r="F44">
-        <v>19.908</v>
+        <v>20.382</v>
       </c>
       <c r="G44">
         <v>1.49</v>
@@ -4889,28 +4889,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M44">
-        <v>1.1009124</v>
+        <v>1.1271246</v>
       </c>
       <c r="N44">
-        <v>4.652420933333334</v>
+        <v>4.626208733333334</v>
       </c>
       <c r="O44">
-        <v>1.2003246008</v>
+        <v>1.1935618532</v>
       </c>
       <c r="P44">
-        <v>3.452096332533333</v>
+        <v>3.432646880133333</v>
       </c>
       <c r="Q44">
-        <v>5.632096332533333</v>
+        <v>5.612646880133333</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1070812523136608</v>
+        <v>0.1079759310963166</v>
       </c>
       <c r="T44">
-        <v>1.415271416019879</v>
+        <v>1.435933743563895</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.2259683271197</v>
+        <v>5.104434179977382</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07919029872490049</v>
+        <v>0.07903977910787777</v>
       </c>
       <c r="C45">
-        <v>25.32064901704432</v>
+        <v>24.95277899813798</v>
       </c>
       <c r="D45">
-        <v>44.21264901704432</v>
+        <v>44.31877899813797</v>
       </c>
       <c r="E45">
-        <v>-7.318000000000001</v>
+        <v>-6.844000000000001</v>
       </c>
       <c r="F45">
-        <v>20.382</v>
+        <v>20.856</v>
       </c>
       <c r="G45">
         <v>1.49</v>
@@ -4971,28 +4971,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M45">
-        <v>1.1271246</v>
+        <v>1.1533368</v>
       </c>
       <c r="N45">
-        <v>4.626208733333334</v>
+        <v>4.599996533333334</v>
       </c>
       <c r="O45">
-        <v>1.1935618532</v>
+        <v>1.1867991056</v>
       </c>
       <c r="P45">
-        <v>3.432646880133333</v>
+        <v>3.413197427733333</v>
       </c>
       <c r="Q45">
-        <v>5.612646880133333</v>
+        <v>5.593197427733333</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1079759310963166</v>
+        <v>0.1089025626926388</v>
       </c>
       <c r="T45">
-        <v>1.435933743563895</v>
+        <v>1.457334011377341</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.104434179977382</v>
+        <v>4.988424312250623</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07903977910787777</v>
+        <v>0.07888925949085501</v>
       </c>
       <c r="C46">
-        <v>24.95277899813798</v>
+        <v>24.58541972336349</v>
       </c>
       <c r="D46">
-        <v>44.31877899813797</v>
+        <v>44.42541972336349</v>
       </c>
       <c r="E46">
-        <v>-6.844000000000001</v>
+        <v>-6.370000000000001</v>
       </c>
       <c r="F46">
-        <v>20.856</v>
+        <v>21.33</v>
       </c>
       <c r="G46">
         <v>1.49</v>
@@ -5053,28 +5053,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M46">
-        <v>1.1533368</v>
+        <v>1.179549</v>
       </c>
       <c r="N46">
-        <v>4.599996533333334</v>
+        <v>4.573784333333334</v>
       </c>
       <c r="O46">
-        <v>1.1867991056</v>
+        <v>1.180036358</v>
       </c>
       <c r="P46">
-        <v>3.413197427733333</v>
+        <v>3.393747975333334</v>
       </c>
       <c r="Q46">
-        <v>5.593197427733333</v>
+        <v>5.573747975333334</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1089025626926388</v>
+        <v>0.1098628899833727</v>
       </c>
       <c r="T46">
-        <v>1.457334011377341</v>
+        <v>1.479512470747638</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.988424312250623</v>
+        <v>4.877570438645053</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07888925949085501</v>
+        <v>0.07873873987383227</v>
       </c>
       <c r="C47">
-        <v>24.58541972336349</v>
+        <v>24.21857488850168</v>
       </c>
       <c r="D47">
-        <v>44.42541972336349</v>
+        <v>44.53257488850168</v>
       </c>
       <c r="E47">
-        <v>-6.370000000000001</v>
+        <v>-5.895999999999997</v>
       </c>
       <c r="F47">
-        <v>21.33</v>
+        <v>21.804</v>
       </c>
       <c r="G47">
         <v>1.49</v>
@@ -5135,28 +5135,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M47">
-        <v>1.179549</v>
+        <v>1.2057612</v>
       </c>
       <c r="N47">
-        <v>4.573784333333334</v>
+        <v>4.547572133333333</v>
       </c>
       <c r="O47">
-        <v>1.180036358</v>
+        <v>1.1732736104</v>
       </c>
       <c r="P47">
-        <v>3.393747975333334</v>
+        <v>3.374298522933334</v>
       </c>
       <c r="Q47">
-        <v>5.573747975333334</v>
+        <v>5.554298522933333</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1098628899833727</v>
+        <v>0.1108587849515412</v>
       </c>
       <c r="T47">
-        <v>1.479512470747638</v>
+        <v>1.502512354539058</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.877570438645053</v>
+        <v>4.771536298674508</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07873873987383227</v>
+        <v>0.07858822025680952</v>
       </c>
       <c r="C48">
-        <v>24.21857488850168</v>
+        <v>23.8522482250769</v>
       </c>
       <c r="D48">
-        <v>44.53257488850168</v>
+        <v>44.6402482250769</v>
       </c>
       <c r="E48">
-        <v>-5.895999999999997</v>
+        <v>-5.421999999999997</v>
       </c>
       <c r="F48">
-        <v>21.804</v>
+        <v>22.278</v>
       </c>
       <c r="G48">
         <v>1.49</v>
@@ -5217,28 +5217,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M48">
-        <v>1.2057612</v>
+        <v>1.2319734</v>
       </c>
       <c r="N48">
-        <v>4.547572133333333</v>
+        <v>4.521359933333334</v>
       </c>
       <c r="O48">
-        <v>1.1732736104</v>
+        <v>1.1665108628</v>
       </c>
       <c r="P48">
-        <v>3.374298522933334</v>
+        <v>3.354849070533334</v>
       </c>
       <c r="Q48">
-        <v>5.554298522933333</v>
+        <v>5.534849070533333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1108587849515412</v>
+        <v>0.1118922608619047</v>
       </c>
       <c r="T48">
-        <v>1.502512354539058</v>
+        <v>1.526380158473551</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.771536298674508</v>
+        <v>4.67001424976654</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07858822025680952</v>
+        <v>0.07843770063978678</v>
       </c>
       <c r="C49">
-        <v>23.8522482250769</v>
+        <v>23.48644350079004</v>
       </c>
       <c r="D49">
-        <v>44.6402482250769</v>
+        <v>44.74844350079004</v>
       </c>
       <c r="E49">
-        <v>-5.421999999999997</v>
+        <v>-4.947999999999997</v>
       </c>
       <c r="F49">
-        <v>22.278</v>
+        <v>22.752</v>
       </c>
       <c r="G49">
         <v>1.49</v>
@@ -5299,28 +5299,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M49">
-        <v>1.2319734</v>
+        <v>1.2581856</v>
       </c>
       <c r="N49">
-        <v>4.521359933333334</v>
+        <v>4.495147733333334</v>
       </c>
       <c r="O49">
-        <v>1.1665108628</v>
+        <v>1.1597481152</v>
       </c>
       <c r="P49">
-        <v>3.354849070533334</v>
+        <v>3.335399618133334</v>
       </c>
       <c r="Q49">
-        <v>5.534849070533333</v>
+        <v>5.515399618133333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1118922608619047</v>
+        <v>0.1129654858457438</v>
       </c>
       <c r="T49">
-        <v>1.526380158473551</v>
+        <v>1.551165954867062</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.67001424976654</v>
+        <v>4.572722286229737</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07843770063978675</v>
+        <v>0.079196131022764</v>
       </c>
       <c r="C50">
-        <v>23.48644350079006</v>
+        <v>22.4725469464325</v>
       </c>
       <c r="D50">
-        <v>44.74844350079005</v>
+        <v>44.2085469464325</v>
       </c>
       <c r="E50">
-        <v>-4.948</v>
+        <v>-4.474</v>
       </c>
       <c r="F50">
-        <v>22.752</v>
+        <v>23.226</v>
       </c>
       <c r="G50">
         <v>1.49</v>
@@ -5381,45 +5381,45 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M50">
-        <v>1.2581856</v>
+        <v>1.3424628</v>
       </c>
       <c r="N50">
-        <v>4.495147733333334</v>
+        <v>4.410870533333334</v>
       </c>
       <c r="O50">
-        <v>1.1597481152</v>
+        <v>1.1380045976</v>
       </c>
       <c r="P50">
-        <v>3.335399618133334</v>
+        <v>3.272865935733334</v>
       </c>
       <c r="Q50">
-        <v>5.515399618133333</v>
+        <v>5.452865935733334</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1129654858457438</v>
+        <v>0.114080798083851</v>
       </c>
       <c r="T50">
-        <v>1.551165954867062</v>
+        <v>1.576923743276005</v>
       </c>
       <c r="U50">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V50">
         <v>0.258</v>
       </c>
       <c r="W50">
-        <v>0.0410326</v>
+        <v>0.0428876</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.572722286229737</v>
+        <v>4.285655686945913</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.079196131022764</v>
+        <v>0.07906416140574127</v>
       </c>
       <c r="C51">
-        <v>22.4725469464325</v>
+        <v>22.09155269736003</v>
       </c>
       <c r="D51">
-        <v>44.2085469464325</v>
+        <v>44.30155269736002</v>
       </c>
       <c r="E51">
-        <v>-4.474</v>
+        <v>-4</v>
       </c>
       <c r="F51">
-        <v>23.226</v>
+        <v>23.7</v>
       </c>
       <c r="G51">
         <v>1.49</v>
@@ -5463,28 +5463,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M51">
-        <v>1.3424628</v>
+        <v>1.36986</v>
       </c>
       <c r="N51">
-        <v>4.410870533333334</v>
+        <v>4.383473333333334</v>
       </c>
       <c r="O51">
-        <v>1.1380045976</v>
+        <v>1.13093612</v>
       </c>
       <c r="P51">
-        <v>3.272865935733334</v>
+        <v>3.252537213333333</v>
       </c>
       <c r="Q51">
-        <v>5.452865935733334</v>
+        <v>5.432537213333333</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.114080798083851</v>
+        <v>0.1152407228114825</v>
       </c>
       <c r="T51">
-        <v>1.576923743276005</v>
+        <v>1.603711843221306</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.285655686945913</v>
+        <v>4.199942573206995</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07906416140574127</v>
+        <v>0.07893219178871852</v>
       </c>
       <c r="C52">
-        <v>22.09155269736003</v>
+        <v>21.71095060349959</v>
       </c>
       <c r="D52">
-        <v>44.30155269736002</v>
+        <v>44.39495060349959</v>
       </c>
       <c r="E52">
-        <v>-4</v>
+        <v>-3.526</v>
       </c>
       <c r="F52">
-        <v>23.7</v>
+        <v>24.174</v>
       </c>
       <c r="G52">
         <v>1.49</v>
@@ -5545,28 +5545,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M52">
-        <v>1.36986</v>
+        <v>1.3972572</v>
       </c>
       <c r="N52">
-        <v>4.383473333333334</v>
+        <v>4.356076133333334</v>
       </c>
       <c r="O52">
-        <v>1.13093612</v>
+        <v>1.1238676424</v>
       </c>
       <c r="P52">
-        <v>3.252537213333333</v>
+        <v>3.232208490933334</v>
       </c>
       <c r="Q52">
-        <v>5.432537213333333</v>
+        <v>5.412208490933334</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1152407228114825</v>
+        <v>0.116447991405548</v>
       </c>
       <c r="T52">
-        <v>1.603711843221306</v>
+        <v>1.631593335001109</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.199942573206995</v>
+        <v>4.117590758046073</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07893219178871852</v>
+        <v>0.07880022217169577</v>
       </c>
       <c r="C53">
-        <v>21.71095060349959</v>
+        <v>21.3307431503525</v>
       </c>
       <c r="D53">
-        <v>44.39495060349959</v>
+        <v>44.4887431503525</v>
       </c>
       <c r="E53">
-        <v>-3.526</v>
+        <v>-3.052</v>
       </c>
       <c r="F53">
-        <v>24.174</v>
+        <v>24.648</v>
       </c>
       <c r="G53">
         <v>1.49</v>
@@ -5627,28 +5627,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M53">
-        <v>1.3972572</v>
+        <v>1.4246544</v>
       </c>
       <c r="N53">
-        <v>4.356076133333334</v>
+        <v>4.328678933333334</v>
       </c>
       <c r="O53">
-        <v>1.1238676424</v>
+        <v>1.1167991648</v>
       </c>
       <c r="P53">
-        <v>3.232208490933334</v>
+        <v>3.211879768533334</v>
       </c>
       <c r="Q53">
-        <v>5.412208490933334</v>
+        <v>5.391879768533334</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.116447991405548</v>
+        <v>0.1177055628576995</v>
       </c>
       <c r="T53">
-        <v>1.631593335001109</v>
+        <v>1.66063655560507</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.117590758046073</v>
+        <v>4.038406320391341</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07880022217169577</v>
+        <v>0.08004466255467302</v>
       </c>
       <c r="C54">
-        <v>21.3307431503525</v>
+        <v>19.98774664488008</v>
       </c>
       <c r="D54">
-        <v>44.4887431503525</v>
+        <v>43.61974664488007</v>
       </c>
       <c r="E54">
-        <v>-3.052</v>
+        <v>-2.577999999999999</v>
       </c>
       <c r="F54">
-        <v>24.648</v>
+        <v>25.122</v>
       </c>
       <c r="G54">
         <v>1.49</v>
@@ -5709,45 +5709,45 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M54">
-        <v>1.4246544</v>
+        <v>1.5399786</v>
       </c>
       <c r="N54">
-        <v>4.328678933333334</v>
+        <v>4.213354733333334</v>
       </c>
       <c r="O54">
-        <v>1.1167991648</v>
+        <v>1.0870455212</v>
       </c>
       <c r="P54">
-        <v>3.211879768533334</v>
+        <v>3.126309212133334</v>
       </c>
       <c r="Q54">
-        <v>5.391879768533334</v>
+        <v>5.306309212133334</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1177055628576995</v>
+        <v>0.119016647988666</v>
       </c>
       <c r="T54">
-        <v>1.66063655560507</v>
+        <v>1.69091565793686</v>
       </c>
       <c r="U54">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V54">
         <v>0.258</v>
       </c>
       <c r="W54">
-        <v>0.0428876</v>
+        <v>0.0454846</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>4.038406320391341</v>
+        <v>3.735982651533817</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08004466255467302</v>
+        <v>0.07993866293765027</v>
       </c>
       <c r="C55">
-        <v>19.98774664488008</v>
+        <v>19.58644162268687</v>
       </c>
       <c r="D55">
-        <v>43.61974664488007</v>
+        <v>43.69244162268686</v>
       </c>
       <c r="E55">
-        <v>-2.577999999999999</v>
+        <v>-2.103999999999999</v>
       </c>
       <c r="F55">
-        <v>25.122</v>
+        <v>25.596</v>
       </c>
       <c r="G55">
         <v>1.49</v>
@@ -5791,28 +5791,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M55">
-        <v>1.5399786</v>
+        <v>1.5690348</v>
       </c>
       <c r="N55">
-        <v>4.213354733333334</v>
+        <v>4.184298533333334</v>
       </c>
       <c r="O55">
-        <v>1.0870455212</v>
+        <v>1.0795490216</v>
       </c>
       <c r="P55">
-        <v>3.126309212133334</v>
+        <v>3.104749511733334</v>
       </c>
       <c r="Q55">
-        <v>5.306309212133334</v>
+        <v>5.284749511733335</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.119016647988666</v>
+        <v>0.1203847368209789</v>
       </c>
       <c r="T55">
-        <v>1.69091565793686</v>
+        <v>1.722511242978727</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.735982651533817</v>
+        <v>3.666797787616523</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07993866293765027</v>
+        <v>0.07983266332062752</v>
       </c>
       <c r="C56">
-        <v>19.58644162268687</v>
+        <v>19.18537930623819</v>
       </c>
       <c r="D56">
-        <v>43.69244162268686</v>
+        <v>43.76537930623819</v>
       </c>
       <c r="E56">
-        <v>-2.103999999999999</v>
+        <v>-1.629999999999999</v>
       </c>
       <c r="F56">
-        <v>25.596</v>
+        <v>26.07</v>
       </c>
       <c r="G56">
         <v>1.49</v>
@@ -5873,28 +5873,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M56">
-        <v>1.5690348</v>
+        <v>1.598091</v>
       </c>
       <c r="N56">
-        <v>4.184298533333334</v>
+        <v>4.155242333333334</v>
       </c>
       <c r="O56">
-        <v>1.0795490216</v>
+        <v>1.072052522</v>
       </c>
       <c r="P56">
-        <v>3.104749511733334</v>
+        <v>3.083189811333334</v>
       </c>
       <c r="Q56">
-        <v>5.284749511733335</v>
+        <v>5.263189811333334</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1203847368209789</v>
+        <v>0.1218136296013945</v>
       </c>
       <c r="T56">
-        <v>1.722511242978727</v>
+        <v>1.755511076244678</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.666797787616523</v>
+        <v>3.600128736932586</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07983266332062752</v>
+        <v>0.07972666370360479</v>
       </c>
       <c r="C57">
-        <v>19.18537930623819</v>
+        <v>18.78456091304407</v>
       </c>
       <c r="D57">
-        <v>43.76537930623819</v>
+        <v>43.83856091304407</v>
       </c>
       <c r="E57">
-        <v>-1.629999999999999</v>
+        <v>-1.155999999999999</v>
       </c>
       <c r="F57">
-        <v>26.07</v>
+        <v>26.544</v>
       </c>
       <c r="G57">
         <v>1.49</v>
@@ -5955,28 +5955,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M57">
-        <v>1.598091</v>
+        <v>1.6271472</v>
       </c>
       <c r="N57">
-        <v>4.155242333333334</v>
+        <v>4.126186133333334</v>
       </c>
       <c r="O57">
-        <v>1.072052522</v>
+        <v>1.0645560224</v>
       </c>
       <c r="P57">
-        <v>3.083189811333334</v>
+        <v>3.061630110933334</v>
       </c>
       <c r="Q57">
-        <v>5.263189811333334</v>
+        <v>5.241630110933334</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1218136296013945</v>
+        <v>0.1233074720536473</v>
       </c>
       <c r="T57">
-        <v>1.755511076244678</v>
+        <v>1.790010901931807</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.600128736932586</v>
+        <v>3.535840723773076</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07972666370360479</v>
+        <v>0.08080489608658203</v>
       </c>
       <c r="C58">
-        <v>18.78456091304407</v>
+        <v>17.57738058679469</v>
       </c>
       <c r="D58">
-        <v>43.83856091304407</v>
+        <v>43.10538058679469</v>
       </c>
       <c r="E58">
-        <v>-1.155999999999999</v>
+        <v>-0.6819999999999986</v>
       </c>
       <c r="F58">
-        <v>26.544</v>
+        <v>27.018</v>
       </c>
       <c r="G58">
         <v>1.49</v>
@@ -6037,45 +6037,45 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M58">
-        <v>1.6271472</v>
+        <v>1.7318538</v>
       </c>
       <c r="N58">
-        <v>4.126186133333334</v>
+        <v>4.021479533333334</v>
       </c>
       <c r="O58">
-        <v>1.0645560224</v>
+        <v>1.0375417196</v>
       </c>
       <c r="P58">
-        <v>3.061630110933334</v>
+        <v>2.983937813733334</v>
       </c>
       <c r="Q58">
-        <v>5.241630110933334</v>
+        <v>5.163937813733334</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1233074720536473</v>
+        <v>0.1248707955501908</v>
       </c>
       <c r="T58">
-        <v>1.790010901931807</v>
+        <v>1.826115370674153</v>
       </c>
       <c r="U58">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V58">
         <v>0.258</v>
       </c>
       <c r="W58">
-        <v>0.0454846</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>3.535840723773076</v>
+        <v>3.322066408453955</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08080489608658203</v>
+        <v>0.0807196724695593</v>
       </c>
       <c r="C59">
-        <v>17.57738058679469</v>
+        <v>17.16043747303705</v>
       </c>
       <c r="D59">
-        <v>43.10538058679469</v>
+        <v>43.16243747303704</v>
       </c>
       <c r="E59">
-        <v>-0.6819999999999986</v>
+        <v>-0.2079999999999984</v>
       </c>
       <c r="F59">
-        <v>27.018</v>
+        <v>27.492</v>
       </c>
       <c r="G59">
         <v>1.49</v>
@@ -6119,28 +6119,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M59">
-        <v>1.7318538</v>
+        <v>1.7622372</v>
       </c>
       <c r="N59">
-        <v>4.021479533333334</v>
+        <v>3.991096133333333</v>
       </c>
       <c r="O59">
-        <v>1.0375417196</v>
+        <v>1.0297028024</v>
       </c>
       <c r="P59">
-        <v>2.983937813733334</v>
+        <v>2.961393330933333</v>
       </c>
       <c r="Q59">
-        <v>5.163937813733334</v>
+        <v>5.141393330933333</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1248707955501908</v>
+        <v>0.1265085630227602</v>
       </c>
       <c r="T59">
-        <v>1.826115370674153</v>
+        <v>1.8639390998328</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.322066408453955</v>
+        <v>3.264789401411645</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0807196724695593</v>
+        <v>0.08063444885253654</v>
       </c>
       <c r="C60">
-        <v>17.16043747303705</v>
+        <v>16.74364560736473</v>
       </c>
       <c r="D60">
-        <v>43.16243747303704</v>
+        <v>43.21964560736473</v>
       </c>
       <c r="E60">
-        <v>-0.208000000000002</v>
+        <v>0.2659999999999982</v>
       </c>
       <c r="F60">
-        <v>27.492</v>
+        <v>27.966</v>
       </c>
       <c r="G60">
         <v>1.49</v>
@@ -6201,28 +6201,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M60">
-        <v>1.7622372</v>
+        <v>1.7926206</v>
       </c>
       <c r="N60">
-        <v>3.991096133333334</v>
+        <v>3.960712733333334</v>
       </c>
       <c r="O60">
-        <v>1.0297028024</v>
+        <v>1.0218638852</v>
       </c>
       <c r="P60">
-        <v>2.961393330933334</v>
+        <v>2.938848848133333</v>
       </c>
       <c r="Q60">
-        <v>5.141393330933334</v>
+        <v>5.118848848133334</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1265085630227602</v>
+        <v>0.1282262215915525</v>
       </c>
       <c r="T60">
-        <v>1.8639390998328</v>
+        <v>1.903607888950405</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.264789401411645</v>
+        <v>3.209453987828397</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08063444885253654</v>
+        <v>0.08054922523551379</v>
       </c>
       <c r="C61">
-        <v>16.74364560736473</v>
+        <v>16.32700559197524</v>
       </c>
       <c r="D61">
-        <v>43.21964560736473</v>
+        <v>43.27700559197523</v>
       </c>
       <c r="E61">
-        <v>0.2659999999999982</v>
+        <v>0.7399999999999984</v>
       </c>
       <c r="F61">
-        <v>27.966</v>
+        <v>28.44</v>
       </c>
       <c r="G61">
         <v>1.49</v>
@@ -6283,28 +6283,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M61">
-        <v>1.7926206</v>
+        <v>1.823004</v>
       </c>
       <c r="N61">
-        <v>3.960712733333334</v>
+        <v>3.930329333333334</v>
       </c>
       <c r="O61">
-        <v>1.0218638852</v>
+        <v>1.014024968</v>
       </c>
       <c r="P61">
-        <v>2.938848848133333</v>
+        <v>2.916304365333334</v>
       </c>
       <c r="Q61">
-        <v>5.118848848133334</v>
+        <v>5.096304365333333</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1282262215915525</v>
+        <v>0.1300297630887845</v>
       </c>
       <c r="T61">
-        <v>1.903607888950405</v>
+        <v>1.945260117523891</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.209453987828397</v>
+        <v>3.155963088031257</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08054922523551379</v>
+        <v>0.08046400161849106</v>
       </c>
       <c r="C62">
-        <v>16.32700559197524</v>
+        <v>15.91051803226722</v>
       </c>
       <c r="D62">
-        <v>43.27700559197523</v>
+        <v>43.33451803226721</v>
       </c>
       <c r="E62">
-        <v>0.7399999999999984</v>
+        <v>1.213999999999999</v>
       </c>
       <c r="F62">
-        <v>28.44</v>
+        <v>28.914</v>
       </c>
       <c r="G62">
         <v>1.49</v>
@@ -6365,28 +6365,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M62">
-        <v>1.823004</v>
+        <v>1.8533874</v>
       </c>
       <c r="N62">
-        <v>3.930329333333334</v>
+        <v>3.899945933333334</v>
       </c>
       <c r="O62">
-        <v>1.014024968</v>
+        <v>1.0061860508</v>
       </c>
       <c r="P62">
-        <v>2.916304365333334</v>
+        <v>2.893759882533334</v>
       </c>
       <c r="Q62">
-        <v>5.096304365333333</v>
+        <v>5.073759882533334</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1300297630887845</v>
+        <v>0.1319257938935668</v>
       </c>
       <c r="T62">
-        <v>1.945260117523891</v>
+        <v>1.989048357819095</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.155963088031257</v>
+        <v>3.104225988227466</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08046400161849106</v>
+        <v>0.08037877800146831</v>
       </c>
       <c r="C63">
-        <v>15.91051803226722</v>
+        <v>15.49418353686177</v>
       </c>
       <c r="D63">
-        <v>43.33451803226721</v>
+        <v>43.39218353686176</v>
       </c>
       <c r="E63">
-        <v>1.213999999999999</v>
+        <v>1.687999999999999</v>
       </c>
       <c r="F63">
-        <v>28.914</v>
+        <v>29.388</v>
       </c>
       <c r="G63">
         <v>1.49</v>
@@ -6447,28 +6447,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M63">
-        <v>1.8533874</v>
+        <v>1.8837708</v>
       </c>
       <c r="N63">
-        <v>3.899945933333334</v>
+        <v>3.869562533333334</v>
       </c>
       <c r="O63">
-        <v>1.0061860508</v>
+        <v>0.9983471336000003</v>
       </c>
       <c r="P63">
-        <v>2.893759882533334</v>
+        <v>2.871215399733334</v>
       </c>
       <c r="Q63">
-        <v>5.073759882533334</v>
+        <v>5.051215399733334</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1319257938935668</v>
+        <v>0.1339216157933376</v>
       </c>
       <c r="T63">
-        <v>1.989048357819095</v>
+        <v>2.035141242340362</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.104225988227466</v>
+        <v>3.054157827127023</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08037877800146831</v>
+        <v>0.08029355438444556</v>
       </c>
       <c r="C64">
-        <v>15.49418353686177</v>
+        <v>15.07800271762389</v>
       </c>
       <c r="D64">
-        <v>43.39218353686176</v>
+        <v>43.45000271762388</v>
       </c>
       <c r="E64">
-        <v>1.687999999999999</v>
+        <v>2.161999999999999</v>
       </c>
       <c r="F64">
-        <v>29.388</v>
+        <v>29.862</v>
       </c>
       <c r="G64">
         <v>1.49</v>
@@ -6529,28 +6529,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M64">
-        <v>1.8837708</v>
+        <v>1.9141542</v>
       </c>
       <c r="N64">
-        <v>3.869562533333334</v>
+        <v>3.839179133333334</v>
       </c>
       <c r="O64">
-        <v>0.9983471336000003</v>
+        <v>0.9905082164000002</v>
       </c>
       <c r="P64">
-        <v>2.871215399733334</v>
+        <v>2.848670916933334</v>
       </c>
       <c r="Q64">
-        <v>5.051215399733334</v>
+        <v>5.028670916933334</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1339216157933376</v>
+        <v>0.136025319957961</v>
       </c>
       <c r="T64">
-        <v>2.035141242340362</v>
+        <v>2.083725634133048</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.054157827127023</v>
+        <v>3.00567913145834</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08029355438444556</v>
+        <v>0.08391239476742282</v>
       </c>
       <c r="C65">
-        <v>15.07800271762389</v>
+        <v>12.27721402448002</v>
       </c>
       <c r="D65">
-        <v>43.45000271762388</v>
+        <v>41.12321402448001</v>
       </c>
       <c r="E65">
-        <v>2.161999999999999</v>
+        <v>2.635999999999999</v>
       </c>
       <c r="F65">
-        <v>29.862</v>
+        <v>30.336</v>
       </c>
       <c r="G65">
         <v>1.49</v>
@@ -6611,45 +6611,45 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M65">
-        <v>1.9141542</v>
+        <v>2.1811584</v>
       </c>
       <c r="N65">
-        <v>3.839179133333334</v>
+        <v>3.572174933333334</v>
       </c>
       <c r="O65">
-        <v>0.9905082164000002</v>
+        <v>0.9216211328000001</v>
       </c>
       <c r="P65">
-        <v>2.848670916933334</v>
+        <v>2.650553800533333</v>
       </c>
       <c r="Q65">
-        <v>5.028670916933334</v>
+        <v>4.830553800533334</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.136025319957961</v>
+        <v>0.1382458965761745</v>
       </c>
       <c r="T65">
-        <v>2.083725634133048</v>
+        <v>2.135009158803106</v>
       </c>
       <c r="U65">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V65">
         <v>0.258</v>
       </c>
       <c r="W65">
-        <v>0.04756220000000001</v>
+        <v>0.0533498</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>3.00567913145834</v>
+        <v>2.637742097654775</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08391239476742282</v>
+        <v>0.08388504715040007</v>
       </c>
       <c r="C66">
-        <v>12.27721402448002</v>
+        <v>11.81986271330911</v>
       </c>
       <c r="D66">
-        <v>41.12321402448001</v>
+        <v>41.13986271330911</v>
       </c>
       <c r="E66">
-        <v>2.635999999999999</v>
+        <v>3.109999999999999</v>
       </c>
       <c r="F66">
-        <v>30.336</v>
+        <v>30.81</v>
       </c>
       <c r="G66">
         <v>1.49</v>
@@ -6693,28 +6693,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M66">
-        <v>2.1811584</v>
+        <v>2.215239</v>
       </c>
       <c r="N66">
-        <v>3.572174933333334</v>
+        <v>3.538094333333334</v>
       </c>
       <c r="O66">
-        <v>0.9216211328000001</v>
+        <v>0.9128283380000002</v>
       </c>
       <c r="P66">
-        <v>2.650553800533333</v>
+        <v>2.625265995333334</v>
       </c>
       <c r="Q66">
-        <v>4.830553800533334</v>
+        <v>4.805265995333334</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1382458965761745</v>
+        <v>0.1405933632868573</v>
       </c>
       <c r="T66">
-        <v>2.135009158803106</v>
+        <v>2.189223170597167</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.637742097654775</v>
+        <v>2.597161449998548</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08388504715040007</v>
+        <v>0.08385769953337732</v>
       </c>
       <c r="C67">
-        <v>11.81986271330911</v>
+        <v>11.36252488800535</v>
       </c>
       <c r="D67">
-        <v>41.13986271330911</v>
+        <v>41.15652488800534</v>
       </c>
       <c r="E67">
-        <v>3.109999999999999</v>
+        <v>3.584</v>
       </c>
       <c r="F67">
-        <v>30.81</v>
+        <v>31.284</v>
       </c>
       <c r="G67">
         <v>1.49</v>
@@ -6775,28 +6775,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M67">
-        <v>2.215239</v>
+        <v>2.2493196</v>
       </c>
       <c r="N67">
-        <v>3.538094333333334</v>
+        <v>3.504013733333334</v>
       </c>
       <c r="O67">
-        <v>0.9128283380000002</v>
+        <v>0.9040355432000001</v>
       </c>
       <c r="P67">
-        <v>2.625265995333334</v>
+        <v>2.599978190133334</v>
       </c>
       <c r="Q67">
-        <v>4.805265995333334</v>
+        <v>4.779978190133334</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1405933632868573</v>
+        <v>0.1430789162746392</v>
       </c>
       <c r="T67">
-        <v>2.189223170597167</v>
+        <v>2.246626241908527</v>
       </c>
       <c r="U67">
         <v>0.07190000000000001</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.597161449998548</v>
+        <v>2.557810518937964</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08385769953337732</v>
+        <v>0.08383035191635457</v>
       </c>
       <c r="C68">
-        <v>11.36252488800535</v>
+        <v>10.90520056496123</v>
       </c>
       <c r="D68">
-        <v>41.15652488800534</v>
+        <v>41.17320056496123</v>
       </c>
       <c r="E68">
-        <v>3.584</v>
+        <v>4.058000000000003</v>
       </c>
       <c r="F68">
-        <v>31.284</v>
+        <v>31.758</v>
       </c>
       <c r="G68">
         <v>1.49</v>
@@ -6857,28 +6857,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M68">
-        <v>2.2493196</v>
+        <v>2.2834002</v>
       </c>
       <c r="N68">
-        <v>3.504013733333334</v>
+        <v>3.469933133333333</v>
       </c>
       <c r="O68">
-        <v>0.9040355432000001</v>
+        <v>0.8952427484000001</v>
       </c>
       <c r="P68">
-        <v>2.599978190133334</v>
+        <v>2.574690384933334</v>
       </c>
       <c r="Q68">
-        <v>4.779978190133334</v>
+        <v>4.754690384933333</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1430789162746392</v>
+        <v>0.1457151088374381</v>
       </c>
       <c r="T68">
-        <v>2.246626241908527</v>
+        <v>2.307508287238756</v>
       </c>
       <c r="U68">
         <v>0.07190000000000001</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.557810518937964</v>
+        <v>2.519634242535904</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08383035191635457</v>
+        <v>0.08577078829933182</v>
       </c>
       <c r="C69">
-        <v>10.90520056496123</v>
+        <v>9.280586064706334</v>
       </c>
       <c r="D69">
-        <v>41.17320056496123</v>
+        <v>40.02258606470633</v>
       </c>
       <c r="E69">
-        <v>4.058000000000003</v>
+        <v>4.532</v>
       </c>
       <c r="F69">
-        <v>31.758</v>
+        <v>32.232</v>
       </c>
       <c r="G69">
         <v>1.49</v>
@@ -6939,45 +6939,45 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M69">
-        <v>2.2834002</v>
+        <v>2.4431856</v>
       </c>
       <c r="N69">
-        <v>3.469933133333333</v>
+        <v>3.310147733333334</v>
       </c>
       <c r="O69">
-        <v>0.8952427484000001</v>
+        <v>0.8540181152000001</v>
       </c>
       <c r="P69">
-        <v>2.574690384933334</v>
+        <v>2.456129618133334</v>
       </c>
       <c r="Q69">
-        <v>4.754690384933333</v>
+        <v>4.636129618133333</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1457151088374381</v>
+        <v>0.148516063435412</v>
       </c>
       <c r="T69">
-        <v>2.307508287238756</v>
+        <v>2.372195460402124</v>
       </c>
       <c r="U69">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V69">
         <v>0.258</v>
       </c>
       <c r="W69">
-        <v>0.0533498</v>
+        <v>0.0562436</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.519634242535904</v>
+        <v>2.354849068090993</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08577078829933182</v>
+        <v>0.08577237868230908</v>
       </c>
       <c r="C70">
-        <v>9.280586064706334</v>
+        <v>8.805669395326326</v>
       </c>
       <c r="D70">
-        <v>40.02258606470633</v>
+        <v>40.02166939532633</v>
       </c>
       <c r="E70">
-        <v>4.532</v>
+        <v>5.006000000000004</v>
       </c>
       <c r="F70">
-        <v>32.232</v>
+        <v>32.706</v>
       </c>
       <c r="G70">
         <v>1.49</v>
@@ -7021,28 +7021,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M70">
-        <v>2.4431856</v>
+        <v>2.479114800000001</v>
       </c>
       <c r="N70">
-        <v>3.310147733333334</v>
+        <v>3.274218533333333</v>
       </c>
       <c r="O70">
-        <v>0.8540181152000001</v>
+        <v>0.8447483816</v>
       </c>
       <c r="P70">
-        <v>2.456129618133334</v>
+        <v>2.429470151733333</v>
       </c>
       <c r="Q70">
-        <v>4.636129618133333</v>
+        <v>4.609470151733333</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.148516063435412</v>
+        <v>0.1514977247816422</v>
       </c>
       <c r="T70">
-        <v>2.372195460402124</v>
+        <v>2.441055999576033</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.354849068090993</v>
+        <v>2.320720820727355</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08577237868230908</v>
+        <v>0.08577396906528632</v>
       </c>
       <c r="C71">
-        <v>8.805669395326326</v>
+        <v>8.330752767935806</v>
       </c>
       <c r="D71">
-        <v>40.02166939532633</v>
+        <v>40.0207527679358</v>
       </c>
       <c r="E71">
-        <v>5.006000000000004</v>
+        <v>5.48</v>
       </c>
       <c r="F71">
-        <v>32.706</v>
+        <v>33.18</v>
       </c>
       <c r="G71">
         <v>1.49</v>
@@ -7103,28 +7103,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M71">
-        <v>2.479114800000001</v>
+        <v>2.515044</v>
       </c>
       <c r="N71">
-        <v>3.274218533333333</v>
+        <v>3.238289333333334</v>
       </c>
       <c r="O71">
-        <v>0.8447483816</v>
+        <v>0.8354786480000002</v>
       </c>
       <c r="P71">
-        <v>2.429470151733333</v>
+        <v>2.402810685333334</v>
       </c>
       <c r="Q71">
-        <v>4.609470151733333</v>
+        <v>4.582810685333333</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1514977247816422</v>
+        <v>0.1546781635509544</v>
       </c>
       <c r="T71">
-        <v>2.441055999576033</v>
+        <v>2.514507241361535</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.320720820727355</v>
+        <v>2.287567666145536</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08577396906528632</v>
+        <v>0.08577555944826359</v>
       </c>
       <c r="C72">
-        <v>8.330752767935806</v>
+        <v>7.855836182531839</v>
       </c>
       <c r="D72">
-        <v>40.0207527679358</v>
+        <v>40.01983618253184</v>
       </c>
       <c r="E72">
-        <v>5.48</v>
+        <v>5.954000000000004</v>
       </c>
       <c r="F72">
-        <v>33.18</v>
+        <v>33.654</v>
       </c>
       <c r="G72">
         <v>1.49</v>
@@ -7185,28 +7185,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M72">
-        <v>2.515044</v>
+        <v>2.5509732</v>
       </c>
       <c r="N72">
-        <v>3.238289333333334</v>
+        <v>3.202360133333333</v>
       </c>
       <c r="O72">
-        <v>0.8354786480000002</v>
+        <v>0.8262089144</v>
       </c>
       <c r="P72">
-        <v>2.402810685333334</v>
+        <v>2.376151218933333</v>
       </c>
       <c r="Q72">
-        <v>4.582810685333333</v>
+        <v>4.556151218933334</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1546781635509544</v>
+        <v>0.1580779429250469</v>
       </c>
       <c r="T72">
-        <v>2.514507241361535</v>
+        <v>2.593024086028797</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.287567666145536</v>
+        <v>2.255348403242078</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08577555944826359</v>
+        <v>0.08577714983124084</v>
       </c>
       <c r="C73">
-        <v>7.855836182531846</v>
+        <v>7.380919639111596</v>
       </c>
       <c r="D73">
-        <v>40.01983618253184</v>
+        <v>40.01891963911159</v>
       </c>
       <c r="E73">
-        <v>5.953999999999997</v>
+        <v>6.428000000000001</v>
       </c>
       <c r="F73">
-        <v>33.654</v>
+        <v>34.128</v>
       </c>
       <c r="G73">
         <v>1.49</v>
@@ -7267,28 +7267,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M73">
-        <v>2.5509732</v>
+        <v>2.5869024</v>
       </c>
       <c r="N73">
-        <v>3.202360133333334</v>
+        <v>3.166430933333334</v>
       </c>
       <c r="O73">
-        <v>0.8262089144000001</v>
+        <v>0.8169391808000002</v>
       </c>
       <c r="P73">
-        <v>2.376151218933334</v>
+        <v>2.349491752533334</v>
       </c>
       <c r="Q73">
-        <v>4.556151218933334</v>
+        <v>4.529491752533334</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1580779429250468</v>
+        <v>0.1617205636830029</v>
       </c>
       <c r="T73">
-        <v>2.593024086028796</v>
+        <v>2.677149276743718</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.255348403242078</v>
+        <v>2.224024119863715</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08577714983124084</v>
+        <v>0.08577874021421809</v>
       </c>
       <c r="C74">
-        <v>7.380919639111596</v>
+        <v>6.906003137672151</v>
       </c>
       <c r="D74">
-        <v>40.01891963911159</v>
+        <v>40.01800313767215</v>
       </c>
       <c r="E74">
-        <v>6.428000000000001</v>
+        <v>6.901999999999997</v>
       </c>
       <c r="F74">
-        <v>34.128</v>
+        <v>34.602</v>
       </c>
       <c r="G74">
         <v>1.49</v>
@@ -7349,28 +7349,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M74">
-        <v>2.5869024</v>
+        <v>2.6228316</v>
       </c>
       <c r="N74">
-        <v>3.166430933333334</v>
+        <v>3.130501733333334</v>
       </c>
       <c r="O74">
-        <v>0.8169391808000002</v>
+        <v>0.8076694472000001</v>
       </c>
       <c r="P74">
-        <v>2.349491752533334</v>
+        <v>2.322832286133334</v>
       </c>
       <c r="Q74">
-        <v>4.529491752533334</v>
+        <v>4.502832286133334</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1617205636830029</v>
+        <v>0.1656330082008077</v>
       </c>
       <c r="T74">
-        <v>2.677149276743718</v>
+        <v>2.767505963067153</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.224024119863715</v>
+        <v>2.193558036029966</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08577874021421809</v>
+        <v>0.08578033059719534</v>
       </c>
       <c r="C75">
-        <v>6.906003137672151</v>
+        <v>6.431086678210633</v>
       </c>
       <c r="D75">
-        <v>40.01800313767215</v>
+        <v>40.01708667821063</v>
       </c>
       <c r="E75">
-        <v>6.901999999999997</v>
+        <v>7.376000000000001</v>
       </c>
       <c r="F75">
-        <v>34.602</v>
+        <v>35.076</v>
       </c>
       <c r="G75">
         <v>1.49</v>
@@ -7431,28 +7431,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M75">
-        <v>2.6228316</v>
+        <v>2.6587608</v>
       </c>
       <c r="N75">
-        <v>3.130501733333334</v>
+        <v>3.094572533333333</v>
       </c>
       <c r="O75">
-        <v>0.8076694472000001</v>
+        <v>0.7983997136000001</v>
       </c>
       <c r="P75">
-        <v>2.322832286133334</v>
+        <v>2.296172819733333</v>
       </c>
       <c r="Q75">
-        <v>4.502832286133334</v>
+        <v>4.476172819733334</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1656330082008077</v>
+        <v>0.1698464099892128</v>
       </c>
       <c r="T75">
-        <v>2.767505963067153</v>
+        <v>2.864813163723161</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.193558036029966</v>
+        <v>2.163915359867398</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08578033059719534</v>
+        <v>0.08578192098017259</v>
       </c>
       <c r="C76">
-        <v>6.431086678210633</v>
+        <v>5.956170260724157</v>
       </c>
       <c r="D76">
-        <v>40.01708667821063</v>
+        <v>40.01617026072415</v>
       </c>
       <c r="E76">
-        <v>7.376000000000001</v>
+        <v>7.849999999999998</v>
       </c>
       <c r="F76">
-        <v>35.076</v>
+        <v>35.55</v>
       </c>
       <c r="G76">
         <v>1.49</v>
@@ -7513,28 +7513,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M76">
-        <v>2.6587608</v>
+        <v>2.69469</v>
       </c>
       <c r="N76">
-        <v>3.094572533333333</v>
+        <v>3.058643333333334</v>
       </c>
       <c r="O76">
-        <v>0.7983997136000001</v>
+        <v>0.7891299800000001</v>
       </c>
       <c r="P76">
-        <v>2.296172819733333</v>
+        <v>2.269513353333334</v>
       </c>
       <c r="Q76">
-        <v>4.476172819733334</v>
+        <v>4.449513353333334</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1698464099892128</v>
+        <v>0.1743968839206904</v>
       </c>
       <c r="T76">
-        <v>2.864813163723161</v>
+        <v>2.969904940431649</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.163915359867398</v>
+        <v>2.135063155069167</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08578192098017259</v>
+        <v>0.08578351136314985</v>
       </c>
       <c r="C77">
-        <v>5.956170260724157</v>
+        <v>5.481253885209838</v>
       </c>
       <c r="D77">
-        <v>40.01617026072415</v>
+        <v>40.01525388520984</v>
       </c>
       <c r="E77">
-        <v>7.849999999999998</v>
+        <v>8.324000000000002</v>
       </c>
       <c r="F77">
-        <v>35.55</v>
+        <v>36.024</v>
       </c>
       <c r="G77">
         <v>1.49</v>
@@ -7595,28 +7595,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M77">
-        <v>2.69469</v>
+        <v>2.7306192</v>
       </c>
       <c r="N77">
-        <v>3.058643333333334</v>
+        <v>3.022714133333333</v>
       </c>
       <c r="O77">
-        <v>0.7891299800000001</v>
+        <v>0.7798602464000001</v>
       </c>
       <c r="P77">
-        <v>2.269513353333334</v>
+        <v>2.242853886933333</v>
       </c>
       <c r="Q77">
-        <v>4.449513353333334</v>
+        <v>4.422853886933334</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1743968839206904</v>
+        <v>0.1793265640131244</v>
       </c>
       <c r="T77">
-        <v>2.969904940431649</v>
+        <v>3.083754365199178</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.135063155069167</v>
+        <v>2.106970218818256</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08578351136314985</v>
+        <v>0.08578510174612711</v>
       </c>
       <c r="C78">
-        <v>5.481253885209838</v>
+        <v>5.006337551664807</v>
       </c>
       <c r="D78">
-        <v>40.01525388520984</v>
+        <v>40.0143375516648</v>
       </c>
       <c r="E78">
-        <v>8.324000000000002</v>
+        <v>8.797999999999998</v>
       </c>
       <c r="F78">
-        <v>36.024</v>
+        <v>36.498</v>
       </c>
       <c r="G78">
         <v>1.49</v>
@@ -7677,28 +7677,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M78">
-        <v>2.7306192</v>
+        <v>2.7665484</v>
       </c>
       <c r="N78">
-        <v>3.022714133333333</v>
+        <v>2.986784933333334</v>
       </c>
       <c r="O78">
-        <v>0.7798602464000001</v>
+        <v>0.7705905128000001</v>
       </c>
       <c r="P78">
-        <v>2.242853886933333</v>
+        <v>2.216194420533334</v>
       </c>
       <c r="Q78">
-        <v>4.422853886933334</v>
+        <v>4.396194420533334</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1793265640131244</v>
+        <v>0.1846849119396831</v>
       </c>
       <c r="T78">
-        <v>3.083754365199178</v>
+        <v>3.207503739946491</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.106970218818256</v>
+        <v>2.079606969223215</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08578510174612711</v>
+        <v>0.08578669212910435</v>
       </c>
       <c r="C79">
-        <v>5.006337551664807</v>
+        <v>4.531421260086162</v>
       </c>
       <c r="D79">
-        <v>40.0143375516648</v>
+        <v>40.01342126008616</v>
       </c>
       <c r="E79">
-        <v>8.797999999999998</v>
+        <v>9.272000000000002</v>
       </c>
       <c r="F79">
-        <v>36.498</v>
+        <v>36.972</v>
       </c>
       <c r="G79">
         <v>1.49</v>
@@ -7759,28 +7759,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M79">
-        <v>2.7665484</v>
+        <v>2.8024776</v>
       </c>
       <c r="N79">
-        <v>2.986784933333334</v>
+        <v>2.950855733333333</v>
       </c>
       <c r="O79">
-        <v>0.7705905128000001</v>
+        <v>0.7613207792000001</v>
       </c>
       <c r="P79">
-        <v>2.216194420533334</v>
+        <v>2.189534954133333</v>
       </c>
       <c r="Q79">
-        <v>4.396194420533334</v>
+        <v>4.369534954133334</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1846849119396831</v>
+        <v>0.1905303824050198</v>
       </c>
       <c r="T79">
-        <v>3.207503739946491</v>
+        <v>3.342503057852652</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.079606969223215</v>
+        <v>2.05294534141266</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08578669212910435</v>
+        <v>0.08578828251208162</v>
       </c>
       <c r="C80">
-        <v>4.531421260086162</v>
+        <v>4.056505010471021</v>
       </c>
       <c r="D80">
-        <v>40.01342126008616</v>
+        <v>40.01250501047102</v>
       </c>
       <c r="E80">
-        <v>9.272000000000002</v>
+        <v>9.745999999999999</v>
       </c>
       <c r="F80">
-        <v>36.972</v>
+        <v>37.446</v>
       </c>
       <c r="G80">
         <v>1.49</v>
@@ -7841,28 +7841,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M80">
-        <v>2.8024776</v>
+        <v>2.8384068</v>
       </c>
       <c r="N80">
-        <v>2.950855733333333</v>
+        <v>2.914926533333334</v>
       </c>
       <c r="O80">
-        <v>0.7613207792000001</v>
+        <v>0.7520510456000001</v>
       </c>
       <c r="P80">
-        <v>2.189534954133333</v>
+        <v>2.162875487733334</v>
       </c>
       <c r="Q80">
-        <v>4.369534954133334</v>
+        <v>4.342875487733334</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1905303824050198</v>
+        <v>0.1969325643432458</v>
       </c>
       <c r="T80">
-        <v>3.342503057852652</v>
+        <v>3.490359453654638</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.05294534141266</v>
+        <v>2.026958691521361</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08578828251208162</v>
+        <v>0.08578987289505886</v>
       </c>
       <c r="C81">
-        <v>4.056505010471021</v>
+        <v>3.581588802816519</v>
       </c>
       <c r="D81">
-        <v>40.01250501047102</v>
+        <v>40.01158880281652</v>
       </c>
       <c r="E81">
-        <v>9.745999999999999</v>
+        <v>10.22</v>
       </c>
       <c r="F81">
-        <v>37.446</v>
+        <v>37.92</v>
       </c>
       <c r="G81">
         <v>1.49</v>
@@ -7923,28 +7923,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M81">
-        <v>2.8384068</v>
+        <v>2.874336</v>
       </c>
       <c r="N81">
-        <v>2.914926533333334</v>
+        <v>2.878997333333333</v>
       </c>
       <c r="O81">
-        <v>0.7520510456000001</v>
+        <v>0.7427813120000001</v>
       </c>
       <c r="P81">
-        <v>2.162875487733334</v>
+        <v>2.136216021333333</v>
       </c>
       <c r="Q81">
-        <v>4.342875487733334</v>
+        <v>4.316216021333334</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1969325643432458</v>
+        <v>0.2039749644752943</v>
       </c>
       <c r="T81">
-        <v>3.490359453654638</v>
+        <v>3.653001489036821</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.026958691521361</v>
+        <v>2.001621707877344</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08578987289505886</v>
+        <v>0.09432594727803612</v>
       </c>
       <c r="C82">
-        <v>3.581588802816519</v>
+        <v>-1.271654345439039</v>
       </c>
       <c r="D82">
-        <v>40.01158880281652</v>
+        <v>35.63234565456096</v>
       </c>
       <c r="E82">
-        <v>10.22</v>
+        <v>10.694</v>
       </c>
       <c r="F82">
-        <v>37.92</v>
+        <v>38.394</v>
       </c>
       <c r="G82">
         <v>1.49</v>
@@ -8005,45 +8005,45 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M82">
-        <v>2.874336</v>
+        <v>3.45546</v>
       </c>
       <c r="N82">
-        <v>2.878997333333333</v>
+        <v>2.297873333333334</v>
       </c>
       <c r="O82">
-        <v>0.7427813120000001</v>
+        <v>0.5928513200000003</v>
       </c>
       <c r="P82">
-        <v>2.136216021333333</v>
+        <v>1.705022013333334</v>
       </c>
       <c r="Q82">
-        <v>4.316216021333334</v>
+        <v>3.885022013333334</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2039749644752943</v>
+        <v>0.2117586698844006</v>
       </c>
       <c r="T82">
-        <v>3.653001489036821</v>
+        <v>3.832763738669761</v>
       </c>
       <c r="U82">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V82">
         <v>0.258</v>
       </c>
       <c r="W82">
-        <v>0.0562436</v>
+        <v>0.06677999999999999</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y82">
-        <v>2.001621707877344</v>
+        <v>1.664997810228836</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09432594727803612</v>
+        <v>0.09443290166101337</v>
       </c>
       <c r="C83">
-        <v>-1.271654345439039</v>
+        <v>-1.794452444186533</v>
       </c>
       <c r="D83">
-        <v>35.63234565456096</v>
+        <v>35.58354755581347</v>
       </c>
       <c r="E83">
-        <v>10.694</v>
+        <v>11.168</v>
       </c>
       <c r="F83">
-        <v>38.394</v>
+        <v>38.868</v>
       </c>
       <c r="G83">
         <v>1.49</v>
@@ -8087,28 +8087,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M83">
-        <v>3.45546</v>
+        <v>3.49812</v>
       </c>
       <c r="N83">
-        <v>2.297873333333334</v>
+        <v>2.255213333333334</v>
       </c>
       <c r="O83">
-        <v>0.5928513200000003</v>
+        <v>0.5818450400000001</v>
       </c>
       <c r="P83">
-        <v>1.705022013333334</v>
+        <v>1.673368293333334</v>
       </c>
       <c r="Q83">
-        <v>3.885022013333334</v>
+        <v>3.853368293333334</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2117586698844006</v>
+        <v>0.2204072314500743</v>
       </c>
       <c r="T83">
-        <v>3.832763738669761</v>
+        <v>4.032499571595251</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.664997810228836</v>
+        <v>1.644692958884582</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09443290166101337</v>
+        <v>0.09453985604399062</v>
       </c>
       <c r="C84">
-        <v>-1.794452444186533</v>
+        <v>-2.317117068824679</v>
       </c>
       <c r="D84">
-        <v>35.58354755581347</v>
+        <v>35.53488293117532</v>
       </c>
       <c r="E84">
-        <v>11.168</v>
+        <v>11.642</v>
       </c>
       <c r="F84">
-        <v>38.868</v>
+        <v>39.342</v>
       </c>
       <c r="G84">
         <v>1.49</v>
@@ -8169,28 +8169,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M84">
-        <v>3.49812</v>
+        <v>3.54078</v>
       </c>
       <c r="N84">
-        <v>2.255213333333334</v>
+        <v>2.212553333333334</v>
       </c>
       <c r="O84">
-        <v>0.5818450400000001</v>
+        <v>0.5708387600000002</v>
       </c>
       <c r="P84">
-        <v>1.673368293333334</v>
+        <v>1.641714573333334</v>
       </c>
       <c r="Q84">
-        <v>3.853368293333334</v>
+        <v>3.821714573333334</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2204072314500743</v>
+        <v>0.2300732708470037</v>
       </c>
       <c r="T84">
-        <v>4.032499571595251</v>
+        <v>4.255733737806091</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.644692958884582</v>
+        <v>1.624877381066696</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09453985604399062</v>
+        <v>0.09464681042696786</v>
       </c>
       <c r="C85">
-        <v>-2.317117068824679</v>
+        <v>-2.839648766229502</v>
       </c>
       <c r="D85">
-        <v>35.53488293117532</v>
+        <v>35.4863512337705</v>
       </c>
       <c r="E85">
-        <v>11.642</v>
+        <v>12.116</v>
       </c>
       <c r="F85">
-        <v>39.342</v>
+        <v>39.816</v>
       </c>
       <c r="G85">
         <v>1.49</v>
@@ -8251,28 +8251,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M85">
-        <v>3.54078</v>
+        <v>3.58344</v>
       </c>
       <c r="N85">
-        <v>2.212553333333334</v>
+        <v>2.169893333333334</v>
       </c>
       <c r="O85">
-        <v>0.5708387600000002</v>
+        <v>0.5598324800000002</v>
       </c>
       <c r="P85">
-        <v>1.641714573333334</v>
+        <v>1.610060853333334</v>
       </c>
       <c r="Q85">
-        <v>3.821714573333334</v>
+        <v>3.790060853333334</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2300732708470037</v>
+        <v>0.2409475651685493</v>
       </c>
       <c r="T85">
-        <v>4.255733737806091</v>
+        <v>4.506872174793287</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.624877381066696</v>
+        <v>1.605533602720663</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09464681042696788</v>
+        <v>0.09475376480994513</v>
       </c>
       <c r="C86">
-        <v>-2.839648766229502</v>
+        <v>-3.362048080293526</v>
       </c>
       <c r="D86">
-        <v>35.48635123377049</v>
+        <v>35.43795191970647</v>
       </c>
       <c r="E86">
-        <v>12.116</v>
+        <v>12.59</v>
       </c>
       <c r="F86">
-        <v>39.816</v>
+        <v>40.29</v>
       </c>
       <c r="G86">
         <v>1.49</v>
@@ -8333,28 +8333,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M86">
-        <v>3.58344</v>
+        <v>3.6261</v>
       </c>
       <c r="N86">
-        <v>2.169893333333334</v>
+        <v>2.127233333333334</v>
       </c>
       <c r="O86">
-        <v>0.5598324800000003</v>
+        <v>0.5488262000000003</v>
       </c>
       <c r="P86">
-        <v>1.610060853333334</v>
+        <v>1.578407133333334</v>
       </c>
       <c r="Q86">
-        <v>3.790060853333334</v>
+        <v>3.758407133333334</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2409475651685492</v>
+        <v>0.2532717653996342</v>
       </c>
       <c r="T86">
-        <v>4.506872174793284</v>
+        <v>4.791495736712107</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.605533602720663</v>
+        <v>1.58664497210042</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09475376480994513</v>
+        <v>0.09486071919292238</v>
       </c>
       <c r="C87">
-        <v>-3.362048080293526</v>
+        <v>-3.884315551946052</v>
       </c>
       <c r="D87">
-        <v>35.43795191970647</v>
+        <v>35.38968444805394</v>
       </c>
       <c r="E87">
-        <v>12.59</v>
+        <v>13.064</v>
       </c>
       <c r="F87">
-        <v>40.29</v>
+        <v>40.764</v>
       </c>
       <c r="G87">
         <v>1.49</v>
@@ -8415,28 +8415,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M87">
-        <v>3.6261</v>
+        <v>3.668759999999999</v>
       </c>
       <c r="N87">
-        <v>2.127233333333334</v>
+        <v>2.084573333333334</v>
       </c>
       <c r="O87">
-        <v>0.5488262000000003</v>
+        <v>0.5378199200000003</v>
       </c>
       <c r="P87">
-        <v>1.578407133333334</v>
+        <v>1.546753413333334</v>
       </c>
       <c r="Q87">
-        <v>3.758407133333334</v>
+        <v>3.726753413333334</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2532717653996342</v>
+        <v>0.2673565656637313</v>
       </c>
       <c r="T87">
-        <v>4.791495736712107</v>
+        <v>5.116779807476474</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.58664497210042</v>
+        <v>1.568195611959718</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09486071919292238</v>
+        <v>0.09496767357589962</v>
       </c>
       <c r="C88">
-        <v>-3.884315551946052</v>
+        <v>-4.40645171917339</v>
       </c>
       <c r="D88">
-        <v>35.38968444805394</v>
+        <v>35.34154828082661</v>
       </c>
       <c r="E88">
-        <v>13.064</v>
+        <v>13.538</v>
       </c>
       <c r="F88">
-        <v>40.764</v>
+        <v>41.238</v>
       </c>
       <c r="G88">
         <v>1.49</v>
@@ -8497,28 +8497,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M88">
-        <v>3.668759999999999</v>
+        <v>3.71142</v>
       </c>
       <c r="N88">
-        <v>2.084573333333334</v>
+        <v>2.041913333333334</v>
       </c>
       <c r="O88">
-        <v>0.5378199200000003</v>
+        <v>0.5268136400000002</v>
       </c>
       <c r="P88">
-        <v>1.546753413333334</v>
+        <v>1.515099693333334</v>
       </c>
       <c r="Q88">
-        <v>3.726753413333334</v>
+        <v>3.695099693333334</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2673565656637313</v>
+        <v>0.283608258276151</v>
       </c>
       <c r="T88">
-        <v>5.116779807476474</v>
+        <v>5.492107581435359</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.568195611959718</v>
+        <v>1.55017037504064</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09496767357589962</v>
+        <v>0.09507462795887689</v>
       </c>
       <c r="C89">
-        <v>-4.40645171917339</v>
+        <v>-4.928457117038782</v>
       </c>
       <c r="D89">
-        <v>35.34154828082661</v>
+        <v>35.29354288296121</v>
       </c>
       <c r="E89">
-        <v>13.538</v>
+        <v>14.012</v>
       </c>
       <c r="F89">
-        <v>41.238</v>
+        <v>41.712</v>
       </c>
       <c r="G89">
         <v>1.49</v>
@@ -8579,28 +8579,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M89">
-        <v>3.71142</v>
+        <v>3.75408</v>
       </c>
       <c r="N89">
-        <v>2.041913333333334</v>
+        <v>1.999253333333334</v>
       </c>
       <c r="O89">
-        <v>0.5268136400000002</v>
+        <v>0.5158073600000003</v>
       </c>
       <c r="P89">
-        <v>1.515099693333334</v>
+        <v>1.483445973333334</v>
       </c>
       <c r="Q89">
-        <v>3.695099693333334</v>
+        <v>3.663445973333334</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.283608258276151</v>
+        <v>0.3025685663239741</v>
       </c>
       <c r="T89">
-        <v>5.492107581435359</v>
+        <v>5.929989984387393</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.55017037504064</v>
+        <v>1.532554802596997</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09507462795887689</v>
+        <v>0.09518158234185413</v>
       </c>
       <c r="C90">
-        <v>-4.928457117038782</v>
+        <v>-5.450332277702245</v>
       </c>
       <c r="D90">
-        <v>35.29354288296121</v>
+        <v>35.24566772229775</v>
       </c>
       <c r="E90">
-        <v>14.012</v>
+        <v>14.486</v>
       </c>
       <c r="F90">
-        <v>41.712</v>
+        <v>42.186</v>
       </c>
       <c r="G90">
         <v>1.49</v>
@@ -8661,28 +8661,28 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M90">
-        <v>3.75408</v>
+        <v>3.79674</v>
       </c>
       <c r="N90">
-        <v>1.999253333333334</v>
+        <v>1.956593333333334</v>
       </c>
       <c r="O90">
-        <v>0.5158073600000003</v>
+        <v>0.5048010800000002</v>
       </c>
       <c r="P90">
-        <v>1.483445973333334</v>
+        <v>1.451792253333334</v>
       </c>
       <c r="Q90">
-        <v>3.663445973333334</v>
+        <v>3.631792253333334</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3025685663239741</v>
+        <v>0.3249762031077649</v>
       </c>
       <c r="T90">
-        <v>5.929989984387393</v>
+        <v>6.447487369694342</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.532554802596997</v>
+        <v>1.515335085713885</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09518158234185413</v>
+        <v>0.1367434675623517</v>
       </c>
       <c r="C91">
-        <v>-5.450332277702245</v>
+        <v>-18.09021084013679</v>
       </c>
       <c r="D91">
-        <v>35.24566772229775</v>
+        <v>23.0797891598632</v>
       </c>
       <c r="E91">
-        <v>14.486</v>
+        <v>14.96</v>
       </c>
       <c r="F91">
-        <v>42.186</v>
+        <v>42.66</v>
       </c>
       <c r="G91">
         <v>1.49</v>
@@ -8743,45 +8743,45 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M91">
-        <v>3.79674</v>
+        <v>6.262488</v>
       </c>
       <c r="N91">
-        <v>1.956593333333334</v>
+        <v>-0.5091546666666664</v>
       </c>
       <c r="O91">
-        <v>0.5048010800000002</v>
+        <v>-0.1313619039999999</v>
       </c>
       <c r="P91">
-        <v>1.451792253333334</v>
+        <v>-0.3777927626666665</v>
       </c>
       <c r="Q91">
-        <v>3.631792253333334</v>
+        <v>1.802207237333334</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3249762031077649</v>
+        <v>0.3593907937669771</v>
       </c>
       <c r="T91">
-        <v>6.447487369694342</v>
+        <v>7.242281611246587</v>
       </c>
       <c r="U91">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.258</v>
+        <v>0.2370240070719497</v>
       </c>
       <c r="W91">
-        <v>0.06677999999999999</v>
+        <v>0.1120048757618378</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y91">
-        <v>1.515335085713885</v>
+        <v>0.9186977018292624</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1367434675623517</v>
+        <v>0.1377534675623517</v>
       </c>
       <c r="C92">
-        <v>-18.09021084013679</v>
+        <v>-18.75619614712215</v>
       </c>
       <c r="D92">
-        <v>23.0797891598632</v>
+        <v>22.88780385287786</v>
       </c>
       <c r="E92">
-        <v>14.96</v>
+        <v>15.434</v>
       </c>
       <c r="F92">
-        <v>42.66</v>
+        <v>43.134</v>
       </c>
       <c r="G92">
         <v>1.49</v>
@@ -8825,37 +8825,37 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M92">
-        <v>6.262488</v>
+        <v>6.332071200000001</v>
       </c>
       <c r="N92">
-        <v>-0.5091546666666664</v>
+        <v>-0.5787378666666667</v>
       </c>
       <c r="O92">
-        <v>-0.1313619039999999</v>
+        <v>-0.1493143696</v>
       </c>
       <c r="P92">
-        <v>-0.3777927626666665</v>
+        <v>-0.4294234970666667</v>
       </c>
       <c r="Q92">
-        <v>1.802207237333334</v>
+        <v>1.750576502933333</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3593907937669771</v>
+        <v>0.3942342152966413</v>
       </c>
       <c r="T92">
-        <v>7.242281611246587</v>
+        <v>8.046979568051764</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2370240070719497</v>
+        <v>0.2344193476535766</v>
       </c>
       <c r="W92">
-        <v>0.1120048757618378</v>
+        <v>0.112387239764455</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.9186977018292624</v>
+        <v>0.9086021226882814</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1377534675623517</v>
+        <v>0.1387634675623517</v>
       </c>
       <c r="C93">
-        <v>-18.75619614712215</v>
+        <v>-19.41901380927227</v>
       </c>
       <c r="D93">
-        <v>22.88780385287786</v>
+        <v>22.69898619072773</v>
       </c>
       <c r="E93">
-        <v>15.434</v>
+        <v>15.908</v>
       </c>
       <c r="F93">
-        <v>43.134</v>
+        <v>43.608</v>
       </c>
       <c r="G93">
         <v>1.49</v>
@@ -8907,37 +8907,37 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M93">
-        <v>6.332071200000001</v>
+        <v>6.401654400000001</v>
       </c>
       <c r="N93">
-        <v>-0.5787378666666667</v>
+        <v>-0.648321066666667</v>
       </c>
       <c r="O93">
-        <v>-0.1493143696</v>
+        <v>-0.1672668352000001</v>
       </c>
       <c r="P93">
-        <v>-0.4294234970666667</v>
+        <v>-0.4810542314666669</v>
       </c>
       <c r="Q93">
-        <v>1.750576502933333</v>
+        <v>1.698945768533333</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3942342152966413</v>
+        <v>0.4377884922087215</v>
       </c>
       <c r="T93">
-        <v>8.046979568051764</v>
+        <v>9.052852014058235</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2344193476535766</v>
+        <v>0.2318713112660377</v>
       </c>
       <c r="W93">
-        <v>0.112387239764455</v>
+        <v>0.1127612915061457</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.9086021226882814</v>
+        <v>0.8987260126590609</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1387634675623517</v>
+        <v>0.1397734675623517</v>
       </c>
       <c r="C94">
-        <v>-19.41901380927227</v>
+        <v>-20.07874158155124</v>
       </c>
       <c r="D94">
-        <v>22.69898619072773</v>
+        <v>22.51325841844876</v>
       </c>
       <c r="E94">
-        <v>15.908</v>
+        <v>16.382</v>
       </c>
       <c r="F94">
-        <v>43.608</v>
+        <v>44.082</v>
       </c>
       <c r="G94">
         <v>1.49</v>
@@ -8989,37 +8989,37 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M94">
-        <v>6.401654400000001</v>
+        <v>6.471237600000001</v>
       </c>
       <c r="N94">
-        <v>-0.648321066666667</v>
+        <v>-0.7179042666666673</v>
       </c>
       <c r="O94">
-        <v>-0.1672668352000001</v>
+        <v>-0.1852193008000002</v>
       </c>
       <c r="P94">
-        <v>-0.4810542314666669</v>
+        <v>-0.5326849658666671</v>
       </c>
       <c r="Q94">
-        <v>1.698945768533333</v>
+        <v>1.647315034133333</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4377884922087215</v>
+        <v>0.493786848238539</v>
       </c>
       <c r="T94">
-        <v>9.052852014058235</v>
+        <v>10.34611658749513</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2318713112660377</v>
+        <v>0.2293780713599513</v>
       </c>
       <c r="W94">
-        <v>0.1127612915061457</v>
+        <v>0.1131272991243592</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8987260126590609</v>
+        <v>0.8890622920928344</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1397734675623517</v>
+        <v>0.1407834675623517</v>
       </c>
       <c r="C95">
-        <v>-20.07874158155124</v>
+        <v>-20.73545469474804</v>
       </c>
       <c r="D95">
-        <v>22.51325841844876</v>
+        <v>22.33054530525196</v>
       </c>
       <c r="E95">
-        <v>16.382</v>
+        <v>16.85600000000001</v>
       </c>
       <c r="F95">
-        <v>44.082</v>
+        <v>44.556</v>
       </c>
       <c r="G95">
         <v>1.49</v>
@@ -9071,37 +9071,37 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M95">
-        <v>6.471237600000001</v>
+        <v>6.540820800000001</v>
       </c>
       <c r="N95">
-        <v>-0.7179042666666673</v>
+        <v>-0.7874874666666676</v>
       </c>
       <c r="O95">
-        <v>-0.1852193008000002</v>
+        <v>-0.2031717664000002</v>
       </c>
       <c r="P95">
-        <v>-0.5326849658666671</v>
+        <v>-0.5843157002666673</v>
       </c>
       <c r="Q95">
-        <v>1.647315034133333</v>
+        <v>1.595684299733333</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.493786848238539</v>
+        <v>0.5684513229449623</v>
       </c>
       <c r="T95">
-        <v>10.34611658749513</v>
+        <v>12.07046935207765</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2293780713599513</v>
+        <v>0.2269378791114411</v>
       </c>
       <c r="W95">
-        <v>0.1131272991243592</v>
+        <v>0.1134855193464405</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8890622920928344</v>
+        <v>0.8796041826024851</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1407834675623517</v>
+        <v>0.1417934675623517</v>
       </c>
       <c r="C96">
-        <v>-20.73545469474804</v>
+        <v>-21.38922595708047</v>
       </c>
       <c r="D96">
-        <v>22.33054530525196</v>
+        <v>22.15077404291953</v>
       </c>
       <c r="E96">
-        <v>16.85600000000001</v>
+        <v>17.33</v>
       </c>
       <c r="F96">
-        <v>44.556</v>
+        <v>45.03</v>
       </c>
       <c r="G96">
         <v>1.49</v>
@@ -9153,37 +9153,37 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M96">
-        <v>6.540820800000001</v>
+        <v>6.610404000000001</v>
       </c>
       <c r="N96">
-        <v>-0.7874874666666676</v>
+        <v>-0.857070666666667</v>
       </c>
       <c r="O96">
-        <v>-0.2031717664000002</v>
+        <v>-0.2211242320000001</v>
       </c>
       <c r="P96">
-        <v>-0.5843157002666673</v>
+        <v>-0.6359464346666669</v>
       </c>
       <c r="Q96">
-        <v>1.595684299733333</v>
+        <v>1.544053565333333</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5684513229449623</v>
+        <v>0.672981587533955</v>
       </c>
       <c r="T96">
-        <v>12.07046935207765</v>
+        <v>14.48456322249319</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2269378791114411</v>
+        <v>0.2245490593313207</v>
       </c>
       <c r="W96">
-        <v>0.1134855193464405</v>
+        <v>0.1138361980901621</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8796041826024851</v>
+        <v>0.8703451912066695</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1417934675623517</v>
+        <v>0.1428034675623517</v>
       </c>
       <c r="C97">
-        <v>-21.38922595708047</v>
+        <v>-22.0401258509305</v>
       </c>
       <c r="D97">
-        <v>22.15077404291953</v>
+        <v>21.97387414906951</v>
       </c>
       <c r="E97">
-        <v>17.33</v>
+        <v>17.80400000000001</v>
       </c>
       <c r="F97">
-        <v>45.03</v>
+        <v>45.504</v>
       </c>
       <c r="G97">
         <v>1.49</v>
@@ -9235,37 +9235,37 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M97">
-        <v>6.610404000000001</v>
+        <v>6.679987200000001</v>
       </c>
       <c r="N97">
-        <v>-0.857070666666667</v>
+        <v>-0.9266538666666673</v>
       </c>
       <c r="O97">
-        <v>-0.2211242320000001</v>
+        <v>-0.2390766976000002</v>
       </c>
       <c r="P97">
-        <v>-0.6359464346666669</v>
+        <v>-0.6875771690666671</v>
       </c>
       <c r="Q97">
-        <v>1.544053565333333</v>
+        <v>1.492422830933333</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.672981587533955</v>
+        <v>0.8297769844174442</v>
       </c>
       <c r="T97">
-        <v>14.48456322249319</v>
+        <v>18.1057040281165</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2245490593313207</v>
+        <v>0.2222100066299528</v>
       </c>
       <c r="W97">
-        <v>0.1138361980901621</v>
+        <v>0.1141795710267229</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8703451912066695</v>
+        <v>0.8612790954649334</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1428034675623517</v>
+        <v>0.1438134675623517</v>
       </c>
       <c r="C98">
-        <v>-22.04012585093049</v>
+        <v>-22.68822262498103</v>
       </c>
       <c r="D98">
-        <v>21.97387414906951</v>
+        <v>21.79977737501896</v>
       </c>
       <c r="E98">
-        <v>17.804</v>
+        <v>18.278</v>
       </c>
       <c r="F98">
-        <v>45.504</v>
+        <v>45.97799999999999</v>
       </c>
       <c r="G98">
         <v>1.49</v>
@@ -9317,37 +9317,37 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M98">
-        <v>6.6799872</v>
+        <v>6.7495704</v>
       </c>
       <c r="N98">
-        <v>-0.9266538666666664</v>
+        <v>-0.9962370666666658</v>
       </c>
       <c r="O98">
-        <v>-0.2390766975999999</v>
+        <v>-0.2570291631999998</v>
       </c>
       <c r="P98">
-        <v>-0.6875771690666664</v>
+        <v>-0.739207903466666</v>
       </c>
       <c r="Q98">
-        <v>1.492422830933334</v>
+        <v>1.440792096533334</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8297769844174421</v>
+        <v>1.091102645889923</v>
       </c>
       <c r="T98">
-        <v>18.10570402811645</v>
+        <v>24.14093870415526</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2222100066299528</v>
+        <v>0.2199191818193348</v>
       </c>
       <c r="W98">
-        <v>0.1141795710267229</v>
+        <v>0.1145158641089217</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8612790954649334</v>
+        <v>0.8523999295323054</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1438134675623517</v>
+        <v>0.1448234675623517</v>
       </c>
       <c r="C99">
-        <v>-22.68822262498103</v>
+        <v>-23.33358238200731</v>
       </c>
       <c r="D99">
-        <v>21.79977737501896</v>
+        <v>21.62841761799269</v>
       </c>
       <c r="E99">
-        <v>18.278</v>
+        <v>18.752</v>
       </c>
       <c r="F99">
-        <v>45.97799999999999</v>
+        <v>46.452</v>
       </c>
       <c r="G99">
         <v>1.49</v>
@@ -9399,37 +9399,37 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M99">
-        <v>6.7495704</v>
+        <v>6.819153600000001</v>
       </c>
       <c r="N99">
-        <v>-0.9962370666666658</v>
+        <v>-1.065820266666667</v>
       </c>
       <c r="O99">
-        <v>-0.2570291631999998</v>
+        <v>-0.2749816288000001</v>
       </c>
       <c r="P99">
-        <v>-0.739207903466666</v>
+        <v>-0.7908386378666669</v>
       </c>
       <c r="Q99">
-        <v>1.440792096533334</v>
+        <v>1.389161362133333</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.091102645889923</v>
+        <v>1.613753968834884</v>
       </c>
       <c r="T99">
-        <v>24.14093870415526</v>
+        <v>36.2114080562329</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2199191818193348</v>
+        <v>0.217675108535464</v>
       </c>
       <c r="W99">
-        <v>0.1145158641089217</v>
+        <v>0.1148452940669939</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8523999295323054</v>
+        <v>0.8437019710676898</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1448234675623517</v>
+        <v>0.1458334675623517</v>
       </c>
       <c r="C100">
-        <v>-23.33358238200731</v>
+        <v>-23.97626916255981</v>
       </c>
       <c r="D100">
-        <v>21.62841761799269</v>
+        <v>21.45973083744018</v>
       </c>
       <c r="E100">
-        <v>18.752</v>
+        <v>19.226</v>
       </c>
       <c r="F100">
-        <v>46.452</v>
+        <v>46.92599999999999</v>
       </c>
       <c r="G100">
         <v>1.49</v>
@@ -9481,37 +9481,37 @@
         <v>5.753333333333334</v>
       </c>
       <c r="M100">
-        <v>6.819153600000001</v>
+        <v>6.8887368</v>
       </c>
       <c r="N100">
-        <v>-1.065820266666667</v>
+        <v>-1.135403466666666</v>
       </c>
       <c r="O100">
-        <v>-0.2749816288000001</v>
+        <v>-0.2929340944</v>
       </c>
       <c r="P100">
-        <v>-0.7908386378666669</v>
+        <v>-0.8424693722666664</v>
       </c>
       <c r="Q100">
-        <v>1.389161362133333</v>
+        <v>1.337530627733334</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.613753968834884</v>
+        <v>3.181707937669768</v>
       </c>
       <c r="T100">
-        <v>36.2114080562329</v>
+        <v>72.4228161124658</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.217675108535464</v>
+        <v>0.2154763700654088</v>
       </c>
       <c r="W100">
-        <v>0.1148452940669939</v>
+        <v>0.115168068874398</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8437019710676898</v>
+        <v>0.835179728935693</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1458334675623517</v>
-      </c>
-      <c r="C101">
-        <v>-23.97626916255981</v>
-      </c>
-      <c r="D101">
-        <v>21.45973083744018</v>
-      </c>
-      <c r="E101">
-        <v>19.226</v>
-      </c>
-      <c r="F101">
-        <v>46.92599999999999</v>
-      </c>
-      <c r="G101">
-        <v>1.49</v>
-      </c>
-      <c r="H101">
-        <v>19.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>7.933333333333334</v>
-      </c>
-      <c r="K101">
-        <v>2.18</v>
-      </c>
-      <c r="L101">
-        <v>5.753333333333334</v>
-      </c>
-      <c r="M101">
-        <v>6.8887368</v>
-      </c>
-      <c r="N101">
-        <v>-1.135403466666666</v>
-      </c>
-      <c r="O101">
-        <v>-0.2929340944</v>
-      </c>
-      <c r="P101">
-        <v>-0.8424693722666664</v>
-      </c>
-      <c r="Q101">
-        <v>1.337530627733334</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.181707937669768</v>
-      </c>
-      <c r="T101">
-        <v>72.4228161124658</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2154763700654088</v>
-      </c>
-      <c r="W101">
-        <v>0.115168068874398</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.835179728935693</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
